--- a/10. LTCS TWR GCU TSN.xlsx
+++ b/10. LTCS TWR GCU TSN.xlsx
@@ -5,26 +5,26 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\app thi thu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\app thi thu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A8A9C3-5A6D-4C6D-999E-DA6C71741A8E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AD6471-FEBE-4CD1-80D2-94964E36DCDE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-94" yWindow="-94" windowWidth="21797" windowHeight="12977" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MIX" sheetId="14" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="11" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">MIX!$A$1:$G$223</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">MIX!$A$1:$G$221</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="800">
   <si>
     <t>530m</t>
   </si>
@@ -3286,7 +3286,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3377,63 +3377,11 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <color indexed="8"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
-    </font>
-    <font>
-      <b/>
-      <strike/>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <strike/>
@@ -3493,7 +3441,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -3516,24 +3464,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3592,9 +3528,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3608,9 +3541,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3643,133 +3573,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -3779,13 +3585,13 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3794,7 +3600,7 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3813,10 +3619,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 2_Air trafic flow" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -4171,21 +3976,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N469"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="25.15" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:N221"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="25.3" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="32.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="63.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="39.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.61328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="63.15234375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.84375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="39.3828125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.3828125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1328125" style="3"/>
+    <col min="9" max="9" width="9.61328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.15234375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="11" customFormat="1" ht="74.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" s="11" customFormat="1" ht="74.599999999999994" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>728</v>
       </c>
@@ -4214,7 +4019,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>609</v>
       </c>
@@ -4243,7 +4048,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A3" s="9" t="s">
         <v>609</v>
       </c>
@@ -4272,7 +4077,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
         <v>609</v>
       </c>
@@ -4301,7 +4106,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
         <v>609</v>
       </c>
@@ -4330,7 +4135,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>609</v>
       </c>
@@ -4359,7 +4164,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="9" t="s">
         <v>609</v>
       </c>
@@ -4388,7 +4193,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
         <v>609</v>
       </c>
@@ -4417,7 +4222,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
         <v>609</v>
       </c>
@@ -4446,7 +4251,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
         <v>609</v>
       </c>
@@ -4475,7 +4280,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="9" t="s">
         <v>609</v>
       </c>
@@ -4504,7 +4309,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
         <v>609</v>
       </c>
@@ -4533,7 +4338,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A13" s="9" t="s">
         <v>609</v>
       </c>
@@ -4562,7 +4367,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A14" s="9" t="s">
         <v>609</v>
       </c>
@@ -4591,7 +4396,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A15" s="9" t="s">
         <v>609</v>
       </c>
@@ -4620,7 +4425,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A16" s="9" t="s">
         <v>299</v>
       </c>
@@ -4649,7 +4454,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="175.9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" ht="177" x14ac:dyDescent="0.4">
       <c r="A17" s="9" t="s">
         <v>299</v>
       </c>
@@ -4678,7 +4483,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A18" s="9" t="s">
         <v>299</v>
       </c>
@@ -4707,7 +4512,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A19" s="9" t="s">
         <v>299</v>
       </c>
@@ -4736,7 +4541,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A20" s="9" t="s">
         <v>299</v>
       </c>
@@ -4765,7 +4570,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A21" s="9" t="s">
         <v>299</v>
       </c>
@@ -4794,7 +4599,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
         <v>299</v>
       </c>
@@ -4823,7 +4628,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A23" s="9" t="s">
         <v>299</v>
       </c>
@@ -4852,7 +4657,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A24" s="9" t="s">
         <v>299</v>
       </c>
@@ -4881,7 +4686,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A25" s="9" t="s">
         <v>299</v>
       </c>
@@ -4910,7 +4715,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A26" s="9" t="s">
         <v>299</v>
       </c>
@@ -4939,7 +4744,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A27" s="9" t="s">
         <v>299</v>
       </c>
@@ -4968,7 +4773,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="150.75" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" ht="151.75" x14ac:dyDescent="0.4">
       <c r="A28" s="9" t="s">
         <v>299</v>
       </c>
@@ -4997,7 +4802,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="175.9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" ht="177" x14ac:dyDescent="0.4">
       <c r="A29" s="9" t="s">
         <v>299</v>
       </c>
@@ -5026,7 +4831,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="150.75" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" ht="151.75" x14ac:dyDescent="0.4">
       <c r="A30" s="9" t="s">
         <v>299</v>
       </c>
@@ -5055,7 +4860,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A31" s="9" t="s">
         <v>299</v>
       </c>
@@ -5084,7 +4889,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A32" s="9" t="s">
         <v>299</v>
       </c>
@@ -5113,7 +4918,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A33" s="9" t="s">
         <v>299</v>
       </c>
@@ -5142,7 +4947,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A34" s="9" t="s">
         <v>611</v>
       </c>
@@ -5171,7 +4976,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A35" s="9" t="s">
         <v>611</v>
       </c>
@@ -5200,7 +5005,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A36" s="9" t="s">
         <v>611</v>
       </c>
@@ -5229,7 +5034,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A37" s="9" t="s">
         <v>611</v>
       </c>
@@ -5258,7 +5063,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A38" s="9" t="s">
         <v>611</v>
       </c>
@@ -5287,7 +5092,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A39" s="9" t="s">
         <v>611</v>
       </c>
@@ -5316,7 +5121,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A40" s="9" t="s">
         <v>611</v>
       </c>
@@ -5345,7 +5150,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A41" s="9" t="s">
         <v>611</v>
       </c>
@@ -5374,7 +5179,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A42" s="9" t="s">
         <v>611</v>
       </c>
@@ -5403,7 +5208,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A43" s="9" t="s">
         <v>611</v>
       </c>
@@ -5430,7 +5235,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A44" s="9" t="s">
         <v>611</v>
       </c>
@@ -5457,7 +5262,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A45" s="9" t="s">
         <v>611</v>
       </c>
@@ -5484,7 +5289,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A46" s="9" t="s">
         <v>611</v>
       </c>
@@ -5511,7 +5316,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A47" s="9" t="s">
         <v>612</v>
       </c>
@@ -5540,7 +5345,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="201" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" ht="202.3" x14ac:dyDescent="0.4">
       <c r="A48" s="9" t="s">
         <v>612</v>
       </c>
@@ -5569,7 +5374,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="201" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" ht="202.3" x14ac:dyDescent="0.4">
       <c r="A49" s="9" t="s">
         <v>612</v>
       </c>
@@ -5598,7 +5403,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="201" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" ht="202.3" x14ac:dyDescent="0.4">
       <c r="A50" s="9" t="s">
         <v>612</v>
       </c>
@@ -5627,7 +5432,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="201" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" ht="202.3" x14ac:dyDescent="0.4">
       <c r="A51" s="9" t="s">
         <v>612</v>
       </c>
@@ -5656,7 +5461,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="201" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" ht="202.3" x14ac:dyDescent="0.4">
       <c r="A52" s="9" t="s">
         <v>612</v>
       </c>
@@ -5685,7 +5490,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="201" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" ht="202.3" x14ac:dyDescent="0.4">
       <c r="A53" s="9" t="s">
         <v>612</v>
       </c>
@@ -5714,7 +5519,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A54" s="9" t="s">
         <v>612</v>
       </c>
@@ -5743,7 +5548,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A55" s="9" t="s">
         <v>612</v>
       </c>
@@ -5772,7 +5577,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A56" s="9" t="s">
         <v>612</v>
       </c>
@@ -5801,7 +5606,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A57" s="9" t="s">
         <v>612</v>
       </c>
@@ -5830,7 +5635,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A58" s="9" t="s">
         <v>612</v>
       </c>
@@ -5859,7 +5664,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A59" s="9" t="s">
         <v>612</v>
       </c>
@@ -5888,7 +5693,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A60" s="9" t="s">
         <v>612</v>
       </c>
@@ -5917,7 +5722,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A61" s="9" t="s">
         <v>612</v>
       </c>
@@ -5946,7 +5751,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A62" s="9" t="s">
         <v>612</v>
       </c>
@@ -5975,7 +5780,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A63" s="9" t="s">
         <v>302</v>
       </c>
@@ -6004,7 +5809,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A64" s="9" t="s">
         <v>302</v>
       </c>
@@ -6033,7 +5838,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A65" s="9" t="s">
         <v>302</v>
       </c>
@@ -6062,7 +5867,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A66" s="9" t="s">
         <v>302</v>
       </c>
@@ -6081,7 +5886,7 @@
       <c r="F66" s="13" t="s">
         <v>629</v>
       </c>
-      <c r="G66" s="21" t="s">
+      <c r="G66" s="20" t="s">
         <v>734</v>
       </c>
       <c r="H66" s="14">
@@ -6091,7 +5896,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A67" s="9" t="s">
         <v>302</v>
       </c>
@@ -6110,7 +5915,7 @@
       <c r="F67" s="13" t="s">
         <v>629</v>
       </c>
-      <c r="G67" s="21" t="s">
+      <c r="G67" s="20" t="s">
         <v>735</v>
       </c>
       <c r="H67" s="14">
@@ -6120,7 +5925,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A68" s="9" t="s">
         <v>302</v>
       </c>
@@ -6136,7 +5941,7 @@
       <c r="E68" s="18">
         <v>250</v>
       </c>
-      <c r="F68" s="22">
+      <c r="F68" s="21">
         <v>233</v>
       </c>
       <c r="G68" s="18">
@@ -6149,7 +5954,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A69" s="9" t="s">
         <v>302</v>
       </c>
@@ -6178,26 +5983,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A70" s="9" t="s">
         <v>302</v>
       </c>
       <c r="B70" s="17">
         <v>8</v>
       </c>
-      <c r="C70" s="36" t="s">
+      <c r="C70" s="34" t="s">
         <v>757</v>
       </c>
-      <c r="D70" s="23">
+      <c r="D70" s="22">
         <v>232</v>
       </c>
-      <c r="E70" s="23">
+      <c r="E70" s="22">
         <v>250</v>
       </c>
-      <c r="F70" s="23">
+      <c r="F70" s="22">
         <v>240</v>
       </c>
-      <c r="G70" s="23">
+      <c r="G70" s="22">
         <v>295</v>
       </c>
       <c r="H70" s="16">
@@ -6207,11 +6012,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="175.9" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:9" ht="177" x14ac:dyDescent="0.4">
       <c r="A71" s="9" t="s">
         <v>613</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B71" s="23">
         <v>1</v>
       </c>
       <c r="C71" s="13" t="s">
@@ -6236,11 +6041,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A72" s="9" t="s">
         <v>613</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B72" s="23">
         <v>2</v>
       </c>
       <c r="C72" s="13" t="s">
@@ -6265,11 +6070,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A73" s="9" t="s">
         <v>613</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B73" s="23">
         <v>3</v>
       </c>
       <c r="C73" s="13" t="s">
@@ -6287,18 +6092,18 @@
       <c r="G73" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="H73" s="25">
+      <c r="H73" s="24">
         <v>4</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A74" s="9" t="s">
         <v>613</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B74" s="23">
         <v>4</v>
       </c>
       <c r="C74" s="13" t="s">
@@ -6323,7 +6128,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A75" s="9" t="s">
         <v>614</v>
       </c>
@@ -6352,65 +6157,65 @@
         <v>796</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A76" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B76" s="14">
         <v>2</v>
       </c>
-      <c r="C76" s="83" t="s">
+      <c r="C76" s="39" t="s">
         <v>522</v>
       </c>
-      <c r="D76" s="83" t="s">
+      <c r="D76" s="39" t="s">
         <v>523</v>
       </c>
-      <c r="E76" s="83" t="s">
+      <c r="E76" s="39" t="s">
         <v>524</v>
       </c>
-      <c r="F76" s="83" t="s">
+      <c r="F76" s="39" t="s">
         <v>767</v>
       </c>
-      <c r="G76" s="83" t="s">
+      <c r="G76" s="39" t="s">
         <v>525</v>
       </c>
-      <c r="H76" s="84">
+      <c r="H76" s="40">
         <v>3</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A77" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B77" s="14">
         <v>3</v>
       </c>
-      <c r="C77" s="83" t="s">
+      <c r="C77" s="39" t="s">
         <v>526</v>
       </c>
-      <c r="D77" s="83" t="s">
+      <c r="D77" s="39" t="s">
         <v>523</v>
       </c>
-      <c r="E77" s="83" t="s">
+      <c r="E77" s="39" t="s">
         <v>527</v>
       </c>
-      <c r="F77" s="86" t="s">
+      <c r="F77" s="42" t="s">
         <v>747</v>
       </c>
-      <c r="G77" s="83" t="s">
+      <c r="G77" s="39" t="s">
         <v>525</v>
       </c>
-      <c r="H77" s="85">
+      <c r="H77" s="41">
         <v>3</v>
       </c>
       <c r="I77" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A78" s="9" t="s">
         <v>614</v>
       </c>
@@ -6426,7 +6231,7 @@
       <c r="E78" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="F78" s="27" t="s">
+      <c r="F78" s="25" t="s">
         <v>293</v>
       </c>
       <c r="G78" s="13" t="s">
@@ -6439,7 +6244,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="121.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:9" ht="121.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="9" t="s">
         <v>614</v>
       </c>
@@ -6449,7 +6254,7 @@
       <c r="C79" s="18" t="s">
         <v>782</v>
       </c>
-      <c r="D79" s="34" t="s">
+      <c r="D79" s="32" t="s">
         <v>554</v>
       </c>
       <c r="E79" s="13" t="s">
@@ -6468,7 +6273,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="9" t="s">
         <v>614</v>
       </c>
@@ -6497,7 +6302,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:14" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A81" s="9" t="s">
         <v>614</v>
       </c>
@@ -6526,36 +6331,36 @@
         <v>796</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:14" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A82" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B82" s="14">
         <v>8</v>
       </c>
-      <c r="C82" s="83" t="s">
+      <c r="C82" s="39" t="s">
         <v>544</v>
       </c>
-      <c r="D82" s="83" t="s">
+      <c r="D82" s="39" t="s">
         <v>531</v>
       </c>
-      <c r="E82" s="83" t="s">
+      <c r="E82" s="39" t="s">
         <v>529</v>
       </c>
-      <c r="F82" s="83" t="s">
+      <c r="F82" s="39" t="s">
         <v>530</v>
       </c>
-      <c r="G82" s="83" t="s">
+      <c r="G82" s="39" t="s">
         <v>532</v>
       </c>
-      <c r="H82" s="85">
+      <c r="H82" s="41">
         <v>3</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:14" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A83" s="9" t="s">
         <v>614</v>
       </c>
@@ -6571,7 +6376,7 @@
       <c r="E83" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="F83" s="27" t="s">
+      <c r="F83" s="25" t="s">
         <v>293</v>
       </c>
       <c r="G83" s="13" t="s">
@@ -6584,7 +6389,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:14" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A84" s="9" t="s">
         <v>614</v>
       </c>
@@ -6613,14 +6418,14 @@
         <v>796</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:14" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A85" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B85" s="14">
         <v>11</v>
       </c>
-      <c r="C85" s="28" t="s">
+      <c r="C85" s="26" t="s">
         <v>604</v>
       </c>
       <c r="D85" s="13" t="s">
@@ -6642,7 +6447,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:14" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A86" s="9" t="s">
         <v>614</v>
       </c>
@@ -6658,7 +6463,7 @@
       <c r="E86" s="13" t="s">
         <v>548</v>
       </c>
-      <c r="F86" s="22" t="s">
+      <c r="F86" s="21" t="s">
         <v>760</v>
       </c>
       <c r="G86" s="13" t="s">
@@ -6671,7 +6476,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:14" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A87" s="9" t="s">
         <v>614</v>
       </c>
@@ -6700,7 +6505,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:14" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A88" s="9" t="s">
         <v>614</v>
       </c>
@@ -6729,7 +6534,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:14" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A89" s="9" t="s">
         <v>614</v>
       </c>
@@ -6745,7 +6550,7 @@
       <c r="E89" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="F89" s="34" t="s">
+      <c r="F89" s="32" t="s">
         <v>746</v>
       </c>
       <c r="G89" s="13" t="s">
@@ -6758,7 +6563,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="201" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:14" ht="202.3" x14ac:dyDescent="0.4">
       <c r="A90" s="9" t="s">
         <v>614</v>
       </c>
@@ -6787,36 +6592,36 @@
         <v>796</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:14" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A91" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="B91" s="85">
+      <c r="B91" s="41">
         <v>17</v>
       </c>
-      <c r="C91" s="83" t="s">
+      <c r="C91" s="39" t="s">
         <v>560</v>
       </c>
-      <c r="D91" s="83" t="s">
+      <c r="D91" s="39" t="s">
         <v>531</v>
       </c>
-      <c r="E91" s="83" t="s">
+      <c r="E91" s="39" t="s">
         <v>529</v>
       </c>
-      <c r="F91" s="83" t="s">
+      <c r="F91" s="39" t="s">
         <v>530</v>
       </c>
-      <c r="G91" s="83" t="s">
+      <c r="G91" s="39" t="s">
         <v>532</v>
       </c>
-      <c r="H91" s="85">
+      <c r="H91" s="41">
         <v>3</v>
       </c>
       <c r="I91" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:14" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A92" s="9" t="s">
         <v>614</v>
       </c>
@@ -6832,7 +6637,7 @@
       <c r="E92" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="F92" s="22" t="s">
+      <c r="F92" s="21" t="s">
         <v>762</v>
       </c>
       <c r="G92" s="13" t="s">
@@ -6844,9 +6649,9 @@
       <c r="I92" s="6" t="s">
         <v>796</v>
       </c>
-      <c r="N92" s="35"/>
-    </row>
-    <row r="93" spans="1:14" ht="100.5" x14ac:dyDescent="0.45">
+      <c r="N92" s="33"/>
+    </row>
+    <row r="93" spans="1:14" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A93" s="9" t="s">
         <v>614</v>
       </c>
@@ -6862,7 +6667,7 @@
       <c r="E93" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="F93" s="22" t="s">
+      <c r="F93" s="21" t="s">
         <v>763</v>
       </c>
       <c r="G93" s="13" t="s">
@@ -6875,7 +6680,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="94" spans="1:14" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:14" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A94" s="9" t="s">
         <v>614</v>
       </c>
@@ -6891,7 +6696,7 @@
       <c r="E94" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="F94" s="27" t="s">
+      <c r="F94" s="25" t="s">
         <v>294</v>
       </c>
       <c r="G94" s="13" t="s">
@@ -6904,7 +6709,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:14" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A95" s="9" t="s">
         <v>614</v>
       </c>
@@ -6920,7 +6725,7 @@
       <c r="E95" s="13" t="s">
         <v>549</v>
       </c>
-      <c r="F95" s="34" t="s">
+      <c r="F95" s="32" t="s">
         <v>745</v>
       </c>
       <c r="G95" s="13" t="s">
@@ -6933,7 +6738,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:14" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A96" s="9" t="s">
         <v>614</v>
       </c>
@@ -6949,7 +6754,7 @@
       <c r="E96" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="F96" s="22" t="s">
+      <c r="F96" s="21" t="s">
         <v>764</v>
       </c>
       <c r="G96" s="13" t="s">
@@ -6962,7 +6767,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A97" s="9" t="s">
         <v>614</v>
       </c>
@@ -6991,94 +6796,94 @@
         <v>796</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A98" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="B98" s="85">
+      <c r="B98" s="41">
         <v>24</v>
       </c>
-      <c r="C98" s="83" t="s">
+      <c r="C98" s="39" t="s">
         <v>546</v>
       </c>
-      <c r="D98" s="83" t="s">
+      <c r="D98" s="39" t="s">
         <v>529</v>
       </c>
-      <c r="E98" s="83" t="s">
+      <c r="E98" s="39" t="s">
         <v>530</v>
       </c>
-      <c r="F98" s="83" t="s">
+      <c r="F98" s="39" t="s">
         <v>531</v>
       </c>
-      <c r="G98" s="83" t="s">
+      <c r="G98" s="39" t="s">
         <v>532</v>
       </c>
-      <c r="H98" s="85">
+      <c r="H98" s="41">
         <v>3</v>
       </c>
       <c r="I98" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A99" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="B99" s="85">
+      <c r="B99" s="41">
         <v>25</v>
       </c>
-      <c r="C99" s="83" t="s">
+      <c r="C99" s="39" t="s">
         <v>567</v>
       </c>
-      <c r="D99" s="83" t="s">
+      <c r="D99" s="39" t="s">
         <v>529</v>
       </c>
-      <c r="E99" s="83" t="s">
+      <c r="E99" s="39" t="s">
         <v>530</v>
       </c>
-      <c r="F99" s="83" t="s">
+      <c r="F99" s="39" t="s">
         <v>531</v>
       </c>
-      <c r="G99" s="83" t="s">
+      <c r="G99" s="39" t="s">
         <v>532</v>
       </c>
-      <c r="H99" s="85">
+      <c r="H99" s="41">
         <v>3</v>
       </c>
       <c r="I99" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A100" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="B100" s="85">
+      <c r="B100" s="41">
         <v>26</v>
       </c>
-      <c r="C100" s="83" t="s">
+      <c r="C100" s="39" t="s">
         <v>528</v>
       </c>
-      <c r="D100" s="83" t="s">
+      <c r="D100" s="39" t="s">
         <v>697</v>
       </c>
-      <c r="E100" s="88" t="s">
+      <c r="E100" s="44" t="s">
         <v>531</v>
       </c>
-      <c r="F100" s="88" t="s">
+      <c r="F100" s="44" t="s">
         <v>744</v>
       </c>
-      <c r="G100" s="83" t="s">
+      <c r="G100" s="39" t="s">
         <v>532</v>
       </c>
-      <c r="H100" s="87">
+      <c r="H100" s="43">
         <v>3</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A101" s="9" t="s">
         <v>614</v>
       </c>
@@ -7100,14 +6905,14 @@
       <c r="G101" s="13" t="s">
         <v>705</v>
       </c>
-      <c r="H101" s="80">
+      <c r="H101" s="36">
         <v>2</v>
       </c>
       <c r="I101" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A102" s="9" t="s">
         <v>614</v>
       </c>
@@ -7129,14 +6934,14 @@
       <c r="G102" s="13" t="s">
         <v>690</v>
       </c>
-      <c r="H102" s="80">
+      <c r="H102" s="36">
         <v>2</v>
       </c>
       <c r="I102" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A103" s="9" t="s">
         <v>614</v>
       </c>
@@ -7158,72 +6963,72 @@
       <c r="G103" s="13" t="s">
         <v>690</v>
       </c>
-      <c r="H103" s="80">
+      <c r="H103" s="36">
         <v>2</v>
       </c>
       <c r="I103" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="99" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:9" ht="99.45" x14ac:dyDescent="0.4">
       <c r="A104" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B104" s="19">
         <v>31</v>
       </c>
-      <c r="C104" s="89" t="s">
+      <c r="C104" s="45" t="s">
         <v>789</v>
       </c>
-      <c r="D104" s="81" t="s">
+      <c r="D104" s="37" t="s">
         <v>709</v>
       </c>
-      <c r="E104" s="81" t="s">
+      <c r="E104" s="37" t="s">
         <v>710</v>
       </c>
-      <c r="F104" s="81" t="s">
+      <c r="F104" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="G104" s="81" t="s">
+      <c r="G104" s="37" t="s">
         <v>708</v>
       </c>
-      <c r="H104" s="82">
+      <c r="H104" s="38">
         <v>2</v>
       </c>
       <c r="I104" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="85.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:9" ht="85.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B105" s="14">
         <v>32</v>
       </c>
-      <c r="C105" s="81" t="s">
+      <c r="C105" s="37" t="s">
         <v>712</v>
       </c>
-      <c r="D105" s="81" t="s">
+      <c r="D105" s="37" t="s">
         <v>710</v>
       </c>
-      <c r="E105" s="81" t="s">
+      <c r="E105" s="37" t="s">
         <v>713</v>
       </c>
-      <c r="F105" s="81" t="s">
+      <c r="F105" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="G105" s="81" t="s">
+      <c r="G105" s="37" t="s">
         <v>708</v>
       </c>
-      <c r="H105" s="82">
+      <c r="H105" s="38">
         <v>1</v>
       </c>
       <c r="I105" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A106" s="9" t="s">
         <v>614</v>
       </c>
@@ -7245,14 +7050,14 @@
       <c r="G106" s="13" t="s">
         <v>716</v>
       </c>
-      <c r="H106" s="80">
+      <c r="H106" s="36">
         <v>2</v>
       </c>
       <c r="I106" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="9" t="s">
         <v>614</v>
       </c>
@@ -7274,437 +7079,437 @@
       <c r="G107" s="13" t="s">
         <v>716</v>
       </c>
-      <c r="H107" s="80">
+      <c r="H107" s="36">
         <v>2</v>
       </c>
       <c r="I107" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="99" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:9" ht="99.45" x14ac:dyDescent="0.4">
       <c r="A108" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B108" s="14">
         <v>35</v>
       </c>
-      <c r="C108" s="81" t="s">
+      <c r="C108" s="37" t="s">
         <v>717</v>
       </c>
-      <c r="D108" s="81" t="s">
+      <c r="D108" s="37" t="s">
         <v>718</v>
       </c>
-      <c r="E108" s="81" t="s">
+      <c r="E108" s="37" t="s">
         <v>713</v>
       </c>
-      <c r="F108" s="81" t="s">
+      <c r="F108" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="G108" s="81" t="s">
+      <c r="G108" s="37" t="s">
         <v>708</v>
       </c>
-      <c r="H108" s="82">
+      <c r="H108" s="38">
         <v>1</v>
       </c>
       <c r="I108" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="99" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:9" ht="99.45" x14ac:dyDescent="0.4">
       <c r="A109" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B109" s="14">
         <v>36</v>
       </c>
-      <c r="C109" s="81" t="s">
+      <c r="C109" s="37" t="s">
         <v>719</v>
       </c>
-      <c r="D109" s="81" t="s">
+      <c r="D109" s="37" t="s">
         <v>718</v>
       </c>
-      <c r="E109" s="81" t="s">
+      <c r="E109" s="37" t="s">
         <v>713</v>
       </c>
-      <c r="F109" s="81" t="s">
+      <c r="F109" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="G109" s="81" t="s">
+      <c r="G109" s="37" t="s">
         <v>708</v>
       </c>
-      <c r="H109" s="82">
+      <c r="H109" s="38">
         <v>1</v>
       </c>
       <c r="I109" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="99" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:9" ht="99.45" x14ac:dyDescent="0.4">
       <c r="A110" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B110" s="14">
         <v>37</v>
       </c>
-      <c r="C110" s="81" t="s">
+      <c r="C110" s="37" t="s">
         <v>720</v>
       </c>
-      <c r="D110" s="81" t="s">
+      <c r="D110" s="37" t="s">
         <v>721</v>
       </c>
-      <c r="E110" s="81" t="s">
+      <c r="E110" s="37" t="s">
         <v>713</v>
       </c>
-      <c r="F110" s="81" t="s">
+      <c r="F110" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="G110" s="81" t="s">
+      <c r="G110" s="37" t="s">
         <v>708</v>
       </c>
-      <c r="H110" s="82">
+      <c r="H110" s="38">
         <v>1</v>
       </c>
       <c r="I110" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="99" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:9" ht="99.45" x14ac:dyDescent="0.4">
       <c r="A111" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B111" s="14">
         <v>38</v>
       </c>
-      <c r="C111" s="81" t="s">
+      <c r="C111" s="37" t="s">
         <v>722</v>
       </c>
-      <c r="D111" s="81" t="s">
+      <c r="D111" s="37" t="s">
         <v>723</v>
       </c>
-      <c r="E111" s="81" t="s">
+      <c r="E111" s="37" t="s">
         <v>713</v>
       </c>
-      <c r="F111" s="81" t="s">
+      <c r="F111" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="G111" s="81" t="s">
+      <c r="G111" s="37" t="s">
         <v>708</v>
       </c>
-      <c r="H111" s="82">
+      <c r="H111" s="38">
         <v>1</v>
       </c>
       <c r="I111" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="106.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:9" ht="106.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B112" s="19">
         <v>39</v>
       </c>
-      <c r="C112" s="89" t="s">
+      <c r="C112" s="45" t="s">
         <v>792</v>
       </c>
-      <c r="D112" s="81" t="s">
+      <c r="D112" s="37" t="s">
         <v>724</v>
       </c>
-      <c r="E112" s="81" t="s">
+      <c r="E112" s="37" t="s">
         <v>723</v>
       </c>
-      <c r="F112" s="81" t="s">
+      <c r="F112" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="G112" s="81" t="s">
+      <c r="G112" s="37" t="s">
         <v>708</v>
       </c>
-      <c r="H112" s="82">
+      <c r="H112" s="38">
         <v>2</v>
       </c>
       <c r="I112" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
-      <c r="A113" s="39" t="s">
+    <row r="113" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
+      <c r="A113" s="35" t="s">
         <v>614</v>
       </c>
-      <c r="B113" s="91">
+      <c r="B113" s="47">
         <v>40</v>
       </c>
-      <c r="C113" s="90" t="s">
+      <c r="C113" s="46" t="s">
         <v>768</v>
       </c>
-      <c r="D113" s="90" t="s">
+      <c r="D113" s="46" t="s">
         <v>684</v>
       </c>
-      <c r="E113" s="90" t="s">
+      <c r="E113" s="46" t="s">
         <v>769</v>
       </c>
-      <c r="F113" s="90" t="s">
+      <c r="F113" s="46" t="s">
         <v>711</v>
       </c>
-      <c r="G113" s="90" t="s">
+      <c r="G113" s="46" t="s">
         <v>770</v>
       </c>
-      <c r="H113" s="91">
+      <c r="H113" s="47">
         <v>1</v>
       </c>
       <c r="I113" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="92.65" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A114" s="39" t="s">
+    <row r="114" spans="1:9" ht="92.7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="35" t="s">
         <v>614</v>
       </c>
-      <c r="B114" s="91">
+      <c r="B114" s="47">
         <v>41</v>
       </c>
-      <c r="C114" s="90" t="s">
+      <c r="C114" s="46" t="s">
         <v>771</v>
       </c>
-      <c r="D114" s="90" t="s">
+      <c r="D114" s="46" t="s">
         <v>688</v>
       </c>
-      <c r="E114" s="90" t="s">
+      <c r="E114" s="46" t="s">
         <v>723</v>
       </c>
-      <c r="F114" s="90" t="s">
+      <c r="F114" s="46" t="s">
         <v>772</v>
       </c>
-      <c r="G114" s="90" t="s">
+      <c r="G114" s="46" t="s">
         <v>770</v>
       </c>
-      <c r="H114" s="91">
+      <c r="H114" s="47">
         <v>1</v>
       </c>
       <c r="I114" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="121.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A115" s="39" t="s">
+    <row r="115" spans="1:9" ht="121.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A115" s="35" t="s">
         <v>614</v>
       </c>
-      <c r="B115" s="91">
+      <c r="B115" s="47">
         <v>42</v>
       </c>
-      <c r="C115" s="90" t="s">
+      <c r="C115" s="46" t="s">
         <v>773</v>
       </c>
-      <c r="D115" s="90" t="s">
+      <c r="D115" s="46" t="s">
         <v>523</v>
       </c>
-      <c r="E115" s="90" t="s">
+      <c r="E115" s="46" t="s">
         <v>769</v>
       </c>
-      <c r="F115" s="90" t="s">
+      <c r="F115" s="46" t="s">
         <v>718</v>
       </c>
-      <c r="G115" s="90" t="s">
+      <c r="G115" s="46" t="s">
         <v>770</v>
       </c>
-      <c r="H115" s="91">
+      <c r="H115" s="47">
         <v>1</v>
       </c>
       <c r="I115" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
-      <c r="A116" s="39" t="s">
+    <row r="116" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
+      <c r="A116" s="35" t="s">
         <v>614</v>
       </c>
-      <c r="B116" s="91">
+      <c r="B116" s="47">
         <v>43</v>
       </c>
-      <c r="C116" s="90" t="s">
+      <c r="C116" s="46" t="s">
         <v>774</v>
       </c>
-      <c r="D116" s="90" t="s">
+      <c r="D116" s="46" t="s">
         <v>707</v>
       </c>
-      <c r="E116" s="90" t="s">
+      <c r="E116" s="46" t="s">
         <v>769</v>
       </c>
-      <c r="F116" s="90" t="s">
+      <c r="F116" s="46" t="s">
         <v>711</v>
       </c>
-      <c r="G116" s="90" t="s">
+      <c r="G116" s="46" t="s">
         <v>770</v>
       </c>
-      <c r="H116" s="91">
+      <c r="H116" s="47">
         <v>1</v>
       </c>
       <c r="I116" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="93.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A117" s="39" t="s">
+    <row r="117" spans="1:9" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="35" t="s">
         <v>614</v>
       </c>
-      <c r="B117" s="91">
+      <c r="B117" s="47">
         <v>44</v>
       </c>
-      <c r="C117" s="90" t="s">
+      <c r="C117" s="46" t="s">
         <v>775</v>
       </c>
-      <c r="D117" s="90" t="s">
+      <c r="D117" s="46" t="s">
         <v>710</v>
       </c>
-      <c r="E117" s="90" t="s">
+      <c r="E117" s="46" t="s">
         <v>776</v>
       </c>
-      <c r="F117" s="90" t="s">
+      <c r="F117" s="46" t="s">
         <v>711</v>
       </c>
-      <c r="G117" s="90" t="s">
+      <c r="G117" s="46" t="s">
         <v>777</v>
       </c>
-      <c r="H117" s="91">
+      <c r="H117" s="47">
         <v>1</v>
       </c>
       <c r="I117" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
-      <c r="A118" s="39" t="s">
+    <row r="118" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
+      <c r="A118" s="35" t="s">
         <v>614</v>
       </c>
-      <c r="B118" s="91">
+      <c r="B118" s="47">
         <v>45</v>
       </c>
-      <c r="C118" s="90" t="s">
+      <c r="C118" s="46" t="s">
         <v>778</v>
       </c>
-      <c r="D118" s="90" t="s">
+      <c r="D118" s="46" t="s">
         <v>707</v>
       </c>
-      <c r="E118" s="90" t="s">
+      <c r="E118" s="46" t="s">
         <v>769</v>
       </c>
-      <c r="F118" s="90" t="s">
+      <c r="F118" s="46" t="s">
         <v>711</v>
       </c>
-      <c r="G118" s="90" t="s">
+      <c r="G118" s="46" t="s">
         <v>770</v>
       </c>
-      <c r="H118" s="91">
+      <c r="H118" s="47">
         <v>1</v>
       </c>
       <c r="I118" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A119" s="39" t="s">
+    <row r="119" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A119" s="35" t="s">
         <v>614</v>
       </c>
-      <c r="B119" s="91">
+      <c r="B119" s="47">
         <v>46</v>
       </c>
-      <c r="C119" s="90" t="s">
+      <c r="C119" s="46" t="s">
         <v>779</v>
       </c>
-      <c r="D119" s="90" t="s">
+      <c r="D119" s="46" t="s">
         <v>710</v>
       </c>
-      <c r="E119" s="90" t="s">
+      <c r="E119" s="46" t="s">
         <v>776</v>
       </c>
-      <c r="F119" s="90" t="s">
+      <c r="F119" s="46" t="s">
         <v>711</v>
       </c>
-      <c r="G119" s="90" t="s">
+      <c r="G119" s="46" t="s">
         <v>777</v>
       </c>
-      <c r="H119" s="91">
+      <c r="H119" s="47">
         <v>1</v>
       </c>
       <c r="I119" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="117" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A120" s="39" t="s">
+    <row r="120" spans="1:9" ht="117" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A120" s="35" t="s">
         <v>614</v>
       </c>
-      <c r="B120" s="91">
+      <c r="B120" s="47">
         <v>47</v>
       </c>
-      <c r="C120" s="90" t="s">
+      <c r="C120" s="46" t="s">
         <v>780</v>
       </c>
-      <c r="D120" s="90" t="s">
+      <c r="D120" s="46" t="s">
         <v>718</v>
       </c>
-      <c r="E120" s="90" t="s">
+      <c r="E120" s="46" t="s">
         <v>524</v>
       </c>
-      <c r="F120" s="90" t="s">
+      <c r="F120" s="46" t="s">
         <v>769</v>
       </c>
-      <c r="G120" s="90" t="s">
+      <c r="G120" s="46" t="s">
         <v>770</v>
       </c>
-      <c r="H120" s="91">
+      <c r="H120" s="47">
         <v>1</v>
       </c>
       <c r="I120" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="114.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A121" s="39" t="s">
+    <row r="121" spans="1:9" ht="114.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="35" t="s">
         <v>614</v>
       </c>
-      <c r="B121" s="91">
+      <c r="B121" s="47">
         <v>48</v>
       </c>
-      <c r="C121" s="90" t="s">
+      <c r="C121" s="46" t="s">
         <v>781</v>
       </c>
-      <c r="D121" s="90" t="s">
+      <c r="D121" s="46" t="s">
         <v>718</v>
       </c>
-      <c r="E121" s="90" t="s">
+      <c r="E121" s="46" t="s">
         <v>769</v>
       </c>
-      <c r="F121" s="90" t="s">
+      <c r="F121" s="46" t="s">
         <v>524</v>
       </c>
-      <c r="G121" s="90" t="s">
+      <c r="G121" s="46" t="s">
         <v>770</v>
       </c>
-      <c r="H121" s="91">
+      <c r="H121" s="47">
         <v>1</v>
       </c>
       <c r="I121" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A122" s="15"/>
       <c r="B122" s="12">
         <v>1</v>
       </c>
-      <c r="C122" s="29" t="s">
+      <c r="C122" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D122" s="29" t="s">
+      <c r="D122" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="E122" s="29" t="s">
+      <c r="E122" s="27" t="s">
         <v>308</v>
       </c>
-      <c r="F122" s="29" t="s">
+      <c r="F122" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="G122" s="30" t="s">
+      <c r="G122" s="28" t="s">
         <v>300</v>
       </c>
       <c r="H122" s="12">
@@ -7714,24 +7519,24 @@
         <v>796</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A123" s="5"/>
       <c r="B123" s="12">
         <v>2</v>
       </c>
-      <c r="C123" s="29" t="s">
+      <c r="C123" s="27" t="s">
         <v>310</v>
       </c>
-      <c r="D123" s="29" t="s">
+      <c r="D123" s="27" t="s">
         <v>311</v>
       </c>
-      <c r="E123" s="29" t="s">
+      <c r="E123" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="F123" s="29" t="s">
+      <c r="F123" s="27" t="s">
         <v>313</v>
       </c>
-      <c r="G123" s="29" t="s">
+      <c r="G123" s="27" t="s">
         <v>300</v>
       </c>
       <c r="H123" s="12">
@@ -7741,24 +7546,24 @@
         <v>796</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="150.75" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:9" ht="151.75" x14ac:dyDescent="0.4">
       <c r="A124" s="16"/>
       <c r="B124" s="12">
         <v>3</v>
       </c>
-      <c r="C124" s="29" t="s">
+      <c r="C124" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="D124" s="29" t="s">
+      <c r="D124" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E124" s="29" t="s">
+      <c r="E124" s="27" t="s">
         <v>316</v>
       </c>
-      <c r="F124" s="29" t="s">
+      <c r="F124" s="27" t="s">
         <v>317</v>
       </c>
-      <c r="G124" s="29" t="s">
+      <c r="G124" s="27" t="s">
         <v>300</v>
       </c>
       <c r="H124" s="12">
@@ -7768,26 +7573,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="150.75" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:9" ht="151.75" x14ac:dyDescent="0.4">
       <c r="A125" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B125" s="12">
         <v>4</v>
       </c>
-      <c r="C125" s="31" t="s">
+      <c r="C125" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="D125" s="30" t="s">
+      <c r="D125" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="E125" s="29" t="s">
+      <c r="E125" s="27" t="s">
         <v>320</v>
       </c>
-      <c r="F125" s="30" t="s">
+      <c r="F125" s="28" t="s">
         <v>321</v>
       </c>
-      <c r="G125" s="30" t="s">
+      <c r="G125" s="28" t="s">
         <v>300</v>
       </c>
       <c r="H125" s="12">
@@ -7797,26 +7602,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A126" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B126" s="12">
         <v>5</v>
       </c>
-      <c r="C126" s="32" t="s">
+      <c r="C126" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="D126" s="29" t="s">
+      <c r="D126" s="27" t="s">
         <v>323</v>
       </c>
-      <c r="E126" s="29" t="s">
+      <c r="E126" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="F126" s="29" t="s">
+      <c r="F126" s="27" t="s">
         <v>325</v>
       </c>
-      <c r="G126" s="29" t="s">
+      <c r="G126" s="27" t="s">
         <v>326</v>
       </c>
       <c r="H126" s="12">
@@ -7826,26 +7631,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A127" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B127" s="12">
         <v>6</v>
       </c>
-      <c r="C127" s="31" t="s">
+      <c r="C127" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="D127" s="29" t="s">
+      <c r="D127" s="27" t="s">
         <v>328</v>
       </c>
-      <c r="E127" s="29" t="s">
+      <c r="E127" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="F127" s="30" t="s">
+      <c r="F127" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="G127" s="29" t="s">
+      <c r="G127" s="27" t="s">
         <v>331</v>
       </c>
       <c r="H127" s="12">
@@ -7855,26 +7660,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A128" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B128" s="12">
         <v>7</v>
       </c>
-      <c r="C128" s="31" t="s">
+      <c r="C128" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="D128" s="29" t="s">
+      <c r="D128" s="27" t="s">
         <v>333</v>
       </c>
-      <c r="E128" s="29" t="s">
+      <c r="E128" s="27" t="s">
         <v>334</v>
       </c>
-      <c r="F128" s="29" t="s">
+      <c r="F128" s="27" t="s">
         <v>335</v>
       </c>
-      <c r="G128" s="29" t="s">
+      <c r="G128" s="27" t="s">
         <v>336</v>
       </c>
       <c r="H128" s="12">
@@ -7884,26 +7689,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:9" ht="49.75" x14ac:dyDescent="0.4">
       <c r="A129" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B129" s="12">
         <v>8</v>
       </c>
-      <c r="C129" s="31" t="s">
+      <c r="C129" s="29" t="s">
         <v>337</v>
       </c>
-      <c r="D129" s="29" t="s">
+      <c r="D129" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="E129" s="29" t="s">
+      <c r="E129" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="F129" s="29" t="s">
+      <c r="F129" s="27" t="s">
         <v>630</v>
       </c>
-      <c r="G129" s="29" t="s">
+      <c r="G129" s="27" t="s">
         <v>303</v>
       </c>
       <c r="H129" s="12">
@@ -7913,26 +7718,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:9" ht="49.75" x14ac:dyDescent="0.4">
       <c r="A130" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B130" s="12">
         <v>9</v>
       </c>
-      <c r="C130" s="31" t="s">
+      <c r="C130" s="29" t="s">
         <v>341</v>
       </c>
-      <c r="D130" s="29" t="s">
+      <c r="D130" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="E130" s="29" t="s">
+      <c r="E130" s="27" t="s">
         <v>340</v>
       </c>
-      <c r="F130" s="29" t="s">
+      <c r="F130" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="G130" s="29" t="s">
+      <c r="G130" s="27" t="s">
         <v>301</v>
       </c>
       <c r="H130" s="12">
@@ -7942,26 +7747,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:9" ht="49.75" x14ac:dyDescent="0.4">
       <c r="A131" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B131" s="12">
         <v>10</v>
       </c>
-      <c r="C131" s="31" t="s">
+      <c r="C131" s="29" t="s">
         <v>342</v>
       </c>
-      <c r="D131" s="29" t="s">
+      <c r="D131" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="E131" s="29" t="s">
+      <c r="E131" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="F131" s="29" t="s">
+      <c r="F131" s="27" t="s">
         <v>340</v>
       </c>
-      <c r="G131" s="29" t="s">
+      <c r="G131" s="27" t="s">
         <v>343</v>
       </c>
       <c r="H131" s="12">
@@ -7971,26 +7776,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A132" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B132" s="12">
         <v>11</v>
       </c>
-      <c r="C132" s="31" t="s">
+      <c r="C132" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="D132" s="29" t="s">
+      <c r="D132" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="E132" s="29" t="s">
+      <c r="E132" s="27" t="s">
         <v>346</v>
       </c>
-      <c r="F132" s="29" t="s">
+      <c r="F132" s="27" t="s">
         <v>347</v>
       </c>
-      <c r="G132" s="29" t="s">
+      <c r="G132" s="27" t="s">
         <v>348</v>
       </c>
       <c r="H132" s="12">
@@ -8000,26 +7805,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A133" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B133" s="12">
         <v>12</v>
       </c>
-      <c r="C133" s="31" t="s">
+      <c r="C133" s="29" t="s">
         <v>349</v>
       </c>
-      <c r="D133" s="29" t="s">
+      <c r="D133" s="27" t="s">
         <v>350</v>
       </c>
-      <c r="E133" s="29" t="s">
+      <c r="E133" s="27" t="s">
         <v>351</v>
       </c>
-      <c r="F133" s="29" t="s">
+      <c r="F133" s="27" t="s">
         <v>352</v>
       </c>
-      <c r="G133" s="29" t="s">
+      <c r="G133" s="27" t="s">
         <v>343</v>
       </c>
       <c r="H133" s="12">
@@ -8029,26 +7834,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:9" ht="49.75" x14ac:dyDescent="0.4">
       <c r="A134" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B134" s="12">
         <v>13</v>
       </c>
-      <c r="C134" s="31" t="s">
+      <c r="C134" s="29" t="s">
         <v>353</v>
       </c>
-      <c r="D134" s="29" t="s">
+      <c r="D134" s="27" t="s">
         <v>633</v>
       </c>
-      <c r="E134" s="29" t="s">
+      <c r="E134" s="27" t="s">
         <v>355</v>
       </c>
-      <c r="F134" s="29" t="s">
+      <c r="F134" s="27" t="s">
         <v>356</v>
       </c>
-      <c r="G134" s="29" t="s">
+      <c r="G134" s="27" t="s">
         <v>343</v>
       </c>
       <c r="H134" s="12">
@@ -8058,26 +7863,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:9" ht="49.75" x14ac:dyDescent="0.4">
       <c r="A135" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B135" s="12">
         <v>14</v>
       </c>
-      <c r="C135" s="31" t="s">
+      <c r="C135" s="29" t="s">
         <v>357</v>
       </c>
-      <c r="D135" s="29" t="s">
+      <c r="D135" s="27" t="s">
         <v>356</v>
       </c>
-      <c r="E135" s="29" t="s">
+      <c r="E135" s="27" t="s">
         <v>356</v>
       </c>
-      <c r="F135" s="29" t="s">
+      <c r="F135" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="G135" s="29" t="s">
+      <c r="G135" s="27" t="s">
         <v>358</v>
       </c>
       <c r="H135" s="12">
@@ -8087,7 +7892,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A136" s="9" t="s">
         <v>305</v>
       </c>
@@ -8116,7 +7921,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A137" s="9" t="s">
         <v>305</v>
       </c>
@@ -8129,7 +7934,7 @@
       <c r="D137" s="13">
         <v>80</v>
       </c>
-      <c r="E137" s="22" t="s">
+      <c r="E137" s="21" t="s">
         <v>748</v>
       </c>
       <c r="F137" s="13">
@@ -8145,7 +7950,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:9" ht="49.75" x14ac:dyDescent="0.4">
       <c r="A138" s="9" t="s">
         <v>305</v>
       </c>
@@ -8174,7 +7979,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:9" ht="49.75" x14ac:dyDescent="0.4">
       <c r="A139" s="9" t="s">
         <v>305</v>
       </c>
@@ -8203,7 +8008,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A140" s="9" t="s">
         <v>305</v>
       </c>
@@ -8232,7 +8037,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="150.75" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:9" ht="151.75" x14ac:dyDescent="0.4">
       <c r="A141" s="9" t="s">
         <v>305</v>
       </c>
@@ -8261,7 +8066,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A142" s="9" t="s">
         <v>305</v>
       </c>
@@ -8290,14 +8095,14 @@
         <v>796</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A143" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B143" s="12">
         <v>22</v>
       </c>
-      <c r="C143" s="28" t="s">
+      <c r="C143" s="26" t="s">
         <v>145</v>
       </c>
       <c r="D143" s="13" t="s">
@@ -8319,7 +8124,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A144" s="9" t="s">
         <v>305</v>
       </c>
@@ -8348,7 +8153,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A145" s="9" t="s">
         <v>305</v>
       </c>
@@ -8377,7 +8182,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A146" s="9" t="s">
         <v>305</v>
       </c>
@@ -8406,7 +8211,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="147" spans="1:9" s="33" customFormat="1" ht="150.75" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:9" s="31" customFormat="1" ht="151.75" x14ac:dyDescent="0.4">
       <c r="A147" s="9" t="s">
         <v>305</v>
       </c>
@@ -8435,7 +8240,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="175.9" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:9" ht="177" x14ac:dyDescent="0.4">
       <c r="A148" s="9" t="s">
         <v>305</v>
       </c>
@@ -8464,7 +8269,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A149" s="9" t="s">
         <v>305</v>
       </c>
@@ -8493,7 +8298,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A150" s="9" t="s">
         <v>305</v>
       </c>
@@ -8522,7 +8327,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A151" s="9" t="s">
         <v>305</v>
       </c>
@@ -8551,7 +8356,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A152" s="9" t="s">
         <v>305</v>
       </c>
@@ -8580,9 +8385,9 @@
         <v>796</v>
       </c>
     </row>
-    <row r="153" spans="1:9" s="7" customFormat="1" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:9" s="7" customFormat="1" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A153" s="15"/>
-      <c r="B153" s="24">
+      <c r="B153" s="23">
         <v>1</v>
       </c>
       <c r="C153" s="13" t="s">
@@ -8607,9 +8412,9 @@
         <v>796</v>
       </c>
     </row>
-    <row r="154" spans="1:9" s="11" customFormat="1" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:9" s="11" customFormat="1" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A154" s="5"/>
-      <c r="B154" s="24">
+      <c r="B154" s="23">
         <v>2</v>
       </c>
       <c r="C154" s="13" t="s">
@@ -8634,7 +8439,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A155" s="15"/>
       <c r="B155" s="17">
         <v>3</v>
@@ -8661,17 +8466,17 @@
         <v>796</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A156" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B156" s="24">
+      <c r="B156" s="23">
         <v>4</v>
       </c>
       <c r="C156" s="13" t="s">
         <v>572</v>
       </c>
-      <c r="D156" s="21" t="s">
+      <c r="D156" s="20" t="s">
         <v>749</v>
       </c>
       <c r="E156" s="13" t="s">
@@ -8690,11 +8495,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A157" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B157" s="24">
+      <c r="B157" s="23">
         <v>5</v>
       </c>
       <c r="C157" s="13" t="s">
@@ -8703,7 +8508,7 @@
       <c r="D157" s="13" t="s">
         <v>692</v>
       </c>
-      <c r="E157" s="21" t="s">
+      <c r="E157" s="20" t="s">
         <v>750</v>
       </c>
       <c r="F157" s="13" t="s">
@@ -8719,7 +8524,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A158" s="9" t="s">
         <v>359</v>
       </c>
@@ -8729,7 +8534,7 @@
       <c r="C158" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="D158" s="21" t="s">
+      <c r="D158" s="20" t="s">
         <v>736</v>
       </c>
       <c r="E158" s="13" t="s">
@@ -8748,11 +8553,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A159" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B159" s="24">
+      <c r="B159" s="23">
         <v>7</v>
       </c>
       <c r="C159" s="13" t="s">
@@ -8761,7 +8566,7 @@
       <c r="D159" s="13" t="s">
         <v>695</v>
       </c>
-      <c r="E159" s="34" t="s">
+      <c r="E159" s="32" t="s">
         <v>696</v>
       </c>
       <c r="F159" s="13" t="s">
@@ -8777,11 +8582,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A160" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B160" s="24">
+      <c r="B160" s="23">
         <v>8</v>
       </c>
       <c r="C160" s="13" t="s">
@@ -8806,7 +8611,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A161" s="9" t="s">
         <v>359</v>
       </c>
@@ -8816,7 +8621,7 @@
       <c r="C161" s="13" t="s">
         <v>580</v>
       </c>
-      <c r="D161" s="34" t="s">
+      <c r="D161" s="32" t="s">
         <v>702</v>
       </c>
       <c r="E161" s="13" t="s">
@@ -8835,11 +8640,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A162" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B162" s="24">
+      <c r="B162" s="23">
         <v>10</v>
       </c>
       <c r="C162" s="13" t="s">
@@ -8864,11 +8669,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A163" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B163" s="24">
+      <c r="B163" s="23">
         <v>11</v>
       </c>
       <c r="C163" s="13" t="s">
@@ -8877,7 +8682,7 @@
       <c r="D163" s="13" t="s">
         <v>695</v>
       </c>
-      <c r="E163" s="21" t="s">
+      <c r="E163" s="20" t="s">
         <v>739</v>
       </c>
       <c r="F163" s="13" t="s">
@@ -8893,7 +8698,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A164" s="9" t="s">
         <v>359</v>
       </c>
@@ -8922,11 +8727,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A165" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B165" s="24">
+      <c r="B165" s="23">
         <v>13</v>
       </c>
       <c r="C165" s="13" t="s">
@@ -8951,17 +8756,17 @@
         <v>796</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A166" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B166" s="24">
+      <c r="B166" s="23">
         <v>14</v>
       </c>
       <c r="C166" s="13" t="s">
         <v>585</v>
       </c>
-      <c r="D166" s="21" t="s">
+      <c r="D166" s="20" t="s">
         <v>743</v>
       </c>
       <c r="E166" s="13" t="s">
@@ -8980,7 +8785,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A167" s="9" t="s">
         <v>359</v>
       </c>
@@ -8999,7 +8804,7 @@
       <c r="F167" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="G167" s="34" t="s">
+      <c r="G167" s="32" t="s">
         <v>703</v>
       </c>
       <c r="H167" s="14">
@@ -9009,11 +8814,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="168" spans="1:9" s="35" customFormat="1" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:9" s="33" customFormat="1" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A168" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B168" s="24">
+      <c r="B168" s="23">
         <v>16</v>
       </c>
       <c r="C168" s="13" t="s">
@@ -9038,11 +8843,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A169" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B169" s="24">
+      <c r="B169" s="23">
         <v>17</v>
       </c>
       <c r="C169" s="18" t="s">
@@ -9060,14 +8865,14 @@
       <c r="G169" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="H169" s="92">
+      <c r="H169" s="48">
         <v>2</v>
       </c>
       <c r="I169" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="170" spans="1:9" s="35" customFormat="1" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:9" s="33" customFormat="1" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A170" s="9" t="s">
         <v>359</v>
       </c>
@@ -9096,11 +8901,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A171" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B171" s="24">
+      <c r="B171" s="23">
         <v>19</v>
       </c>
       <c r="C171" s="13" t="s">
@@ -9125,11 +8930,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A172" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B172" s="24">
+      <c r="B172" s="23">
         <v>20</v>
       </c>
       <c r="C172" s="13" t="s">
@@ -9138,7 +8943,7 @@
       <c r="D172" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="E172" s="34" t="s">
+      <c r="E172" s="32" t="s">
         <v>704</v>
       </c>
       <c r="F172" s="13" t="s">
@@ -9154,7 +8959,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="9" t="s">
         <v>359</v>
       </c>
@@ -9183,11 +8988,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="175.9" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:9" ht="202.3" x14ac:dyDescent="0.4">
       <c r="A174" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B174" s="24">
+      <c r="B174" s="23">
         <v>22</v>
       </c>
       <c r="C174" s="13" t="s">
@@ -9212,11 +9017,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A175" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B175" s="24">
+      <c r="B175" s="23">
         <v>23</v>
       </c>
       <c r="C175" s="13" t="s">
@@ -9241,7 +9046,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A176" s="9" t="s">
         <v>359</v>
       </c>
@@ -9270,11 +9075,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A177" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B177" s="24">
+      <c r="B177" s="23">
         <v>25</v>
       </c>
       <c r="C177" s="13" t="s">
@@ -9299,11 +9104,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="201" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:9" ht="202.3" x14ac:dyDescent="0.4">
       <c r="A178" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B178" s="24">
+      <c r="B178" s="23">
         <v>26</v>
       </c>
       <c r="C178" s="13" t="s">
@@ -9326,7 +9131,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A179" s="9" t="s">
         <v>359</v>
       </c>
@@ -9353,11 +9158,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A180" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B180" s="24">
+      <c r="B180" s="23">
         <v>28</v>
       </c>
       <c r="C180" s="13" t="s">
@@ -9382,11 +9187,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A181" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B181" s="24">
+      <c r="B181" s="23">
         <v>29</v>
       </c>
       <c r="C181" s="13" t="s">
@@ -9411,7 +9216,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="150.75" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:9" ht="151.75" x14ac:dyDescent="0.4">
       <c r="A182" s="9" t="s">
         <v>359</v>
       </c>
@@ -9438,11 +9243,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A183" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B183" s="24">
+      <c r="B183" s="23">
         <v>31</v>
       </c>
       <c r="C183" s="13" t="s">
@@ -9467,11 +9272,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A184" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B184" s="24">
+      <c r="B184" s="23">
         <v>32</v>
       </c>
       <c r="C184" s="13" t="s">
@@ -9496,7 +9301,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A185" s="9" t="s">
         <v>359</v>
       </c>
@@ -9525,11 +9330,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A186" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B186" s="24">
+      <c r="B186" s="23">
         <v>34</v>
       </c>
       <c r="C186" s="13" t="s">
@@ -9554,11 +9359,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="150.75" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:9" ht="151.75" x14ac:dyDescent="0.4">
       <c r="A187" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B187" s="24">
+      <c r="B187" s="23">
         <v>35</v>
       </c>
       <c r="C187" s="13" t="s">
@@ -9583,7 +9388,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A188" s="9" t="s">
         <v>359</v>
       </c>
@@ -9612,11 +9417,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A189" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B189" s="24">
+      <c r="B189" s="23">
         <v>37</v>
       </c>
       <c r="C189" s="13" t="s">
@@ -9641,11 +9446,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A190" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B190" s="24">
+      <c r="B190" s="23">
         <v>38</v>
       </c>
       <c r="C190" s="13" t="s">
@@ -9670,7 +9475,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A191" s="9" t="s">
         <v>359</v>
       </c>
@@ -9699,11 +9504,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A192" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B192" s="24">
+      <c r="B192" s="23">
         <v>40</v>
       </c>
       <c r="C192" s="13" t="s">
@@ -9728,11 +9533,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A193" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B193" s="24">
+      <c r="B193" s="23">
         <v>41</v>
       </c>
       <c r="C193" s="13" t="s">
@@ -9757,7 +9562,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A194" s="9" t="s">
         <v>359</v>
       </c>
@@ -9786,11 +9591,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A195" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B195" s="24">
+      <c r="B195" s="23">
         <v>43</v>
       </c>
       <c r="C195" s="13" t="s">
@@ -9815,11 +9620,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="175.9" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:9" ht="177" x14ac:dyDescent="0.4">
       <c r="A196" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B196" s="24">
+      <c r="B196" s="23">
         <v>44</v>
       </c>
       <c r="C196" s="13" t="s">
@@ -9844,7 +9649,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A197" s="9" t="s">
         <v>359</v>
       </c>
@@ -9873,11 +9678,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A198" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B198" s="24">
+      <c r="B198" s="23">
         <v>46</v>
       </c>
       <c r="C198" s="13" t="s">
@@ -9902,11 +9707,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A199" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B199" s="24">
+      <c r="B199" s="23">
         <v>47</v>
       </c>
       <c r="C199" s="13" t="s">
@@ -9931,7 +9736,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A200" s="9" t="s">
         <v>359</v>
       </c>
@@ -9960,11 +9765,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="100.5" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A201" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B201" s="24">
+      <c r="B201" s="23">
         <v>49</v>
       </c>
       <c r="C201" s="13" t="s">
@@ -9987,11 +9792,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A202" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B202" s="24">
+      <c r="B202" s="23">
         <v>50</v>
       </c>
       <c r="C202" s="13" t="s">
@@ -10016,7 +9821,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A203" s="9" t="s">
         <v>359</v>
       </c>
@@ -10045,26 +9850,26 @@
         <v>796</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A204" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B204" s="24">
+      <c r="B204" s="23">
         <v>52</v>
       </c>
       <c r="C204" s="13" t="s">
         <v>635</v>
       </c>
-      <c r="D204" s="23" t="s">
+      <c r="D204" s="22" t="s">
         <v>636</v>
       </c>
-      <c r="E204" s="23" t="s">
+      <c r="E204" s="22" t="s">
         <v>637</v>
       </c>
-      <c r="F204" s="23" t="s">
+      <c r="F204" s="22" t="s">
         <v>638</v>
       </c>
-      <c r="G204" s="23" t="s">
+      <c r="G204" s="22" t="s">
         <v>639</v>
       </c>
       <c r="H204" s="16">
@@ -10074,11 +9879,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="150.75" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:9" ht="151.75" x14ac:dyDescent="0.4">
       <c r="A205" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B205" s="24">
+      <c r="B205" s="23">
         <v>53</v>
       </c>
       <c r="C205" s="13" t="s">
@@ -10103,7 +9908,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="150.75" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:9" ht="151.75" x14ac:dyDescent="0.4">
       <c r="A206" s="9" t="s">
         <v>359</v>
       </c>
@@ -10132,11 +9937,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A207" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B207" s="24">
+      <c r="B207" s="23">
         <v>55</v>
       </c>
       <c r="C207" s="13" t="s">
@@ -10161,11 +9966,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="251.25" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:9" ht="252.9" x14ac:dyDescent="0.4">
       <c r="A208" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B208" s="24">
+      <c r="B208" s="23">
         <v>56</v>
       </c>
       <c r="C208" s="13" t="s">
@@ -10190,7 +9995,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="125.65" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:9" ht="126.45" x14ac:dyDescent="0.4">
       <c r="A209" s="9" t="s">
         <v>359</v>
       </c>
@@ -10219,11 +10024,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="150.75" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:9" ht="151.75" x14ac:dyDescent="0.4">
       <c r="A210" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B210" s="24">
+      <c r="B210" s="23">
         <v>58</v>
       </c>
       <c r="C210" s="13" t="s">
@@ -10248,11 +10053,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="175.9" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:9" ht="177" x14ac:dyDescent="0.4">
       <c r="A211" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B211" s="24">
+      <c r="B211" s="23">
         <v>59</v>
       </c>
       <c r="C211" s="13" t="s">
@@ -10277,7 +10082,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="50.25" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:9" ht="50.6" x14ac:dyDescent="0.4">
       <c r="A212" s="9" t="s">
         <v>359</v>
       </c>
@@ -10306,11 +10111,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A213" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B213" s="24">
+      <c r="B213" s="23">
         <v>61</v>
       </c>
       <c r="C213" s="13" t="s">
@@ -10335,7 +10140,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A214" s="9" t="s">
         <v>359</v>
       </c>
@@ -10345,7 +10150,7 @@
       <c r="C214" s="18" t="s">
         <v>766</v>
       </c>
-      <c r="D214" s="22" t="s">
+      <c r="D214" s="21" t="s">
         <v>710</v>
       </c>
       <c r="E214" s="13" t="s">
@@ -10364,7 +10169,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A215" s="9" t="s">
         <v>359</v>
       </c>
@@ -10393,11 +10198,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A216" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B216" s="24">
+      <c r="B216" s="23">
         <v>64</v>
       </c>
       <c r="C216" s="13" t="s">
@@ -10422,11 +10227,11 @@
         <v>796</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:9" ht="75.900000000000006" x14ac:dyDescent="0.4">
       <c r="A217" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B217" s="24">
+      <c r="B217" s="23">
         <v>65</v>
       </c>
       <c r="C217" s="13" t="s">
@@ -10451,7 +10256,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="75.400000000000006" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:9" ht="101.15" x14ac:dyDescent="0.4">
       <c r="A218" s="9" t="s">
         <v>359</v>
       </c>
@@ -10480,3041 +10285,96 @@
         <v>796</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A219" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B219" s="24">
+      <c r="B219" s="23">
         <v>67</v>
       </c>
-      <c r="C219" s="34" t="s">
+      <c r="C219" s="32" t="s">
         <v>573</v>
       </c>
-      <c r="D219" s="34" t="s">
+      <c r="D219" s="32" t="s">
         <v>725</v>
       </c>
-      <c r="E219" s="34" t="s">
+      <c r="E219" s="32" t="s">
         <v>693</v>
       </c>
-      <c r="F219" s="34" t="s">
+      <c r="F219" s="32" t="s">
         <v>574</v>
       </c>
-      <c r="G219" s="34" t="s">
+      <c r="G219" s="32" t="s">
         <v>696</v>
       </c>
-      <c r="H219" s="93">
+      <c r="H219" s="49">
         <v>1</v>
       </c>
       <c r="I219" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A220" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B220" s="24">
+      <c r="B220" s="23">
         <v>68</v>
       </c>
-      <c r="C220" s="34" t="s">
+      <c r="C220" s="32" t="s">
         <v>586</v>
       </c>
-      <c r="D220" s="34" t="s">
+      <c r="D220" s="32" t="s">
         <v>694</v>
       </c>
-      <c r="E220" s="34" t="s">
+      <c r="E220" s="32" t="s">
         <v>726</v>
       </c>
-      <c r="F220" s="34" t="s">
+      <c r="F220" s="32" t="s">
         <v>574</v>
       </c>
-      <c r="G220" s="34" t="s">
+      <c r="G220" s="32" t="s">
         <v>696</v>
       </c>
-      <c r="H220" s="93">
+      <c r="H220" s="49">
         <v>2</v>
       </c>
       <c r="I220" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="9" t="s">
         <v>359</v>
       </c>
       <c r="B221" s="17">
         <v>69</v>
       </c>
-      <c r="C221" s="34" t="s">
+      <c r="C221" s="32" t="s">
         <v>587</v>
       </c>
-      <c r="D221" s="34" t="s">
+      <c r="D221" s="32" t="s">
         <v>727</v>
       </c>
-      <c r="E221" s="34" t="s">
+      <c r="E221" s="32" t="s">
         <v>694</v>
       </c>
-      <c r="F221" s="34" t="s">
+      <c r="F221" s="32" t="s">
         <v>574</v>
       </c>
-      <c r="G221" s="34" t="s">
+      <c r="G221" s="32" t="s">
         <v>696</v>
       </c>
-      <c r="H221" s="93">
+      <c r="H221" s="49">
         <v>1</v>
       </c>
       <c r="I221" s="6" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A222" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="B222" s="37"/>
-      <c r="C222" s="38"/>
-      <c r="D222" s="38"/>
-      <c r="E222" s="38"/>
-      <c r="F222" s="38"/>
-      <c r="G222" s="38"/>
-      <c r="H222" s="39"/>
-      <c r="I222" s="6" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A223" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="B223" s="37"/>
-      <c r="C223" s="38"/>
-      <c r="D223" s="38"/>
-      <c r="E223" s="38"/>
-      <c r="F223" s="38"/>
-      <c r="G223" s="38"/>
-      <c r="H223" s="39"/>
-      <c r="I223" s="6"/>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A224" s="9" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A225" s="9"/>
-      <c r="B225" s="57"/>
-      <c r="C225" s="56"/>
-      <c r="D225" s="56"/>
-      <c r="E225" s="56"/>
-      <c r="F225" s="56"/>
-      <c r="G225" s="56"/>
-      <c r="H225" s="56"/>
-      <c r="I225" s="40"/>
-      <c r="J225" s="77"/>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A226" s="9"/>
-      <c r="B226" s="8"/>
-      <c r="C226" s="8"/>
-      <c r="D226" s="8"/>
-      <c r="E226" s="8"/>
-      <c r="F226" s="8"/>
-      <c r="G226" s="8"/>
-      <c r="H226" s="8"/>
-      <c r="I226" s="40"/>
-      <c r="J226" s="77"/>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B227" s="51"/>
-      <c r="C227" s="13"/>
-      <c r="D227" s="13"/>
-      <c r="E227" s="13"/>
-      <c r="F227" s="13"/>
-      <c r="G227" s="13"/>
-      <c r="H227" s="25"/>
-      <c r="I227" s="40"/>
-      <c r="J227" s="77"/>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A228" s="58"/>
-      <c r="B228" s="50"/>
-      <c r="C228" s="13"/>
-      <c r="D228" s="13"/>
-      <c r="E228" s="13"/>
-      <c r="F228" s="13"/>
-      <c r="G228" s="13"/>
-      <c r="H228" s="25"/>
-      <c r="I228" s="40"/>
-      <c r="J228" s="77"/>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A229" s="8"/>
-      <c r="B229" s="51"/>
-      <c r="C229" s="13"/>
-      <c r="D229" s="13"/>
-      <c r="E229" s="13"/>
-      <c r="F229" s="13"/>
-      <c r="G229" s="13"/>
-      <c r="H229" s="25"/>
-      <c r="I229" s="40"/>
-      <c r="J229" s="77"/>
-    </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A230" s="8"/>
-      <c r="B230" s="50"/>
-      <c r="C230" s="13"/>
-      <c r="D230" s="13"/>
-      <c r="E230" s="13"/>
-      <c r="F230" s="13"/>
-      <c r="G230" s="13"/>
-      <c r="H230" s="25"/>
-      <c r="I230" s="40"/>
-      <c r="J230" s="77"/>
-    </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A231" s="8"/>
-      <c r="B231" s="51"/>
-      <c r="C231" s="13"/>
-      <c r="D231" s="13"/>
-      <c r="E231" s="13"/>
-      <c r="F231" s="13"/>
-      <c r="G231" s="13"/>
-      <c r="H231" s="25"/>
-      <c r="I231" s="40"/>
-      <c r="J231" s="77"/>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A232" s="8"/>
-      <c r="B232" s="50"/>
-      <c r="C232" s="13"/>
-      <c r="D232" s="13"/>
-      <c r="E232" s="13"/>
-      <c r="F232" s="13"/>
-      <c r="G232" s="13"/>
-      <c r="H232" s="25"/>
-      <c r="I232" s="40"/>
-      <c r="J232" s="77"/>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A233" s="8"/>
-      <c r="B233" s="51"/>
-      <c r="C233" s="13"/>
-      <c r="D233" s="13"/>
-      <c r="E233" s="13"/>
-      <c r="F233" s="13"/>
-      <c r="G233" s="13"/>
-      <c r="H233" s="25"/>
-      <c r="I233" s="40"/>
-      <c r="J233" s="77"/>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A234" s="8"/>
-      <c r="B234" s="50"/>
-      <c r="C234" s="13"/>
-      <c r="D234" s="13"/>
-      <c r="E234" s="13"/>
-      <c r="F234" s="13"/>
-      <c r="G234" s="13"/>
-      <c r="H234" s="25"/>
-      <c r="I234" s="40"/>
-      <c r="J234" s="77"/>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A235" s="8"/>
-      <c r="B235" s="51"/>
-      <c r="C235" s="13"/>
-      <c r="D235" s="13"/>
-      <c r="E235" s="13"/>
-      <c r="F235" s="13"/>
-      <c r="G235" s="13"/>
-      <c r="H235" s="25"/>
-      <c r="I235" s="40"/>
-      <c r="J235" s="77"/>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A236" s="8"/>
-      <c r="B236" s="52"/>
-      <c r="C236" s="18"/>
-      <c r="D236" s="13"/>
-      <c r="E236" s="13"/>
-      <c r="F236" s="13"/>
-      <c r="G236" s="13"/>
-      <c r="H236" s="25"/>
-      <c r="I236" s="53"/>
-      <c r="J236" s="77"/>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A237" s="8"/>
-      <c r="B237" s="51"/>
-      <c r="C237" s="13"/>
-      <c r="D237" s="13"/>
-      <c r="E237" s="13"/>
-      <c r="F237" s="13"/>
-      <c r="G237" s="13"/>
-      <c r="H237" s="25"/>
-      <c r="I237" s="40"/>
-      <c r="J237" s="77"/>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A238" s="8"/>
-      <c r="B238" s="50"/>
-      <c r="C238" s="13"/>
-      <c r="D238" s="13"/>
-      <c r="E238" s="13"/>
-      <c r="F238" s="13"/>
-      <c r="G238" s="13"/>
-      <c r="H238" s="25"/>
-      <c r="I238" s="40"/>
-      <c r="J238" s="77"/>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A239" s="8"/>
-      <c r="B239" s="54"/>
-      <c r="C239" s="18"/>
-      <c r="D239" s="18"/>
-      <c r="E239" s="22"/>
-      <c r="F239" s="13"/>
-      <c r="G239" s="13"/>
-      <c r="H239" s="25"/>
-      <c r="I239" s="53"/>
-      <c r="J239" s="77"/>
-    </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A240" s="8"/>
-      <c r="B240" s="52"/>
-      <c r="C240" s="18"/>
-      <c r="D240" s="13"/>
-      <c r="E240" s="13"/>
-      <c r="F240" s="13"/>
-      <c r="G240" s="13"/>
-      <c r="H240" s="25"/>
-      <c r="I240" s="53"/>
-      <c r="J240" s="77"/>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A241" s="8"/>
-      <c r="B241" s="52"/>
-      <c r="C241" s="18"/>
-      <c r="D241" s="13"/>
-      <c r="E241" s="13"/>
-      <c r="F241" s="13"/>
-      <c r="G241" s="13"/>
-      <c r="H241" s="25"/>
-      <c r="I241" s="53"/>
-      <c r="J241" s="77"/>
-    </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A242" s="8"/>
-      <c r="B242" s="54"/>
-      <c r="C242" s="18"/>
-      <c r="D242" s="13"/>
-      <c r="E242" s="13"/>
-      <c r="F242" s="13"/>
-      <c r="G242" s="13"/>
-      <c r="H242" s="25"/>
-      <c r="I242" s="53"/>
-      <c r="J242" s="77"/>
-    </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A243" s="8"/>
-      <c r="B243" s="52"/>
-      <c r="C243" s="18"/>
-      <c r="D243" s="13"/>
-      <c r="E243" s="13"/>
-      <c r="F243" s="13"/>
-      <c r="G243" s="13"/>
-      <c r="H243" s="25"/>
-      <c r="I243" s="53"/>
-      <c r="J243" s="77"/>
-    </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A244" s="8"/>
-      <c r="B244" s="51"/>
-      <c r="C244" s="13"/>
-      <c r="D244" s="13"/>
-      <c r="E244" s="13"/>
-      <c r="F244" s="13"/>
-      <c r="G244" s="13"/>
-      <c r="H244" s="25"/>
-      <c r="I244" s="40"/>
-      <c r="J244" s="77"/>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A245" s="8"/>
-      <c r="B245" s="50"/>
-      <c r="C245" s="13"/>
-      <c r="D245" s="13"/>
-      <c r="E245" s="13"/>
-      <c r="F245" s="13"/>
-      <c r="G245" s="13"/>
-      <c r="H245" s="25"/>
-      <c r="I245" s="40"/>
-      <c r="J245" s="77"/>
-    </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A246" s="8"/>
-      <c r="B246" s="57"/>
-      <c r="C246" s="56"/>
-      <c r="D246" s="56"/>
-      <c r="E246" s="56"/>
-      <c r="F246" s="56"/>
-      <c r="G246" s="56"/>
-      <c r="H246" s="56"/>
-      <c r="I246" s="55"/>
-      <c r="J246" s="78"/>
-    </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A247" s="8"/>
-      <c r="B247" s="8"/>
-      <c r="C247" s="8"/>
-      <c r="D247" s="8"/>
-      <c r="E247" s="8"/>
-      <c r="F247" s="8"/>
-      <c r="G247" s="8"/>
-      <c r="H247" s="8"/>
-      <c r="I247" s="40"/>
-      <c r="J247" s="77"/>
-    </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A248" s="8"/>
-      <c r="B248" s="51"/>
-      <c r="C248" s="13"/>
-      <c r="D248" s="13"/>
-      <c r="E248" s="13"/>
-      <c r="F248" s="13"/>
-      <c r="G248" s="13"/>
-      <c r="H248" s="25"/>
-      <c r="I248" s="40"/>
-      <c r="J248" s="77"/>
-    </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A249" s="58"/>
-      <c r="B249" s="8"/>
-      <c r="C249" s="13"/>
-      <c r="D249" s="13"/>
-      <c r="E249" s="13"/>
-      <c r="F249" s="13"/>
-      <c r="G249" s="13"/>
-      <c r="H249" s="25"/>
-      <c r="I249" s="40"/>
-      <c r="J249" s="77"/>
-    </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A250" s="8"/>
-      <c r="B250" s="51"/>
-      <c r="C250" s="13"/>
-      <c r="D250" s="13"/>
-      <c r="E250" s="13"/>
-      <c r="F250" s="13"/>
-      <c r="G250" s="13"/>
-      <c r="H250" s="25"/>
-      <c r="I250" s="40"/>
-      <c r="J250" s="77"/>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A251" s="8"/>
-      <c r="B251" s="8"/>
-      <c r="C251" s="13"/>
-      <c r="D251" s="13"/>
-      <c r="E251" s="13"/>
-      <c r="F251" s="13"/>
-      <c r="G251" s="13"/>
-      <c r="H251" s="25"/>
-      <c r="I251" s="40"/>
-      <c r="J251" s="77"/>
-    </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A252" s="8"/>
-      <c r="B252" s="54"/>
-      <c r="C252" s="18"/>
-      <c r="D252" s="18"/>
-      <c r="E252" s="13"/>
-      <c r="F252" s="13"/>
-      <c r="G252" s="13"/>
-      <c r="H252" s="25"/>
-      <c r="I252" s="53"/>
-      <c r="J252" s="77"/>
-    </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A253" s="8"/>
-      <c r="B253" s="76"/>
-      <c r="C253" s="18"/>
-      <c r="D253" s="18"/>
-      <c r="E253" s="13"/>
-      <c r="F253" s="13"/>
-      <c r="G253" s="13"/>
-      <c r="H253" s="25"/>
-      <c r="I253" s="53"/>
-      <c r="J253" s="77"/>
-    </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A254" s="8"/>
-      <c r="B254" s="54"/>
-      <c r="C254" s="18"/>
-      <c r="D254" s="18"/>
-      <c r="E254" s="13"/>
-      <c r="F254" s="13"/>
-      <c r="G254" s="13"/>
-      <c r="H254" s="25"/>
-      <c r="I254" s="53"/>
-      <c r="J254" s="77"/>
-    </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A255" s="8"/>
-      <c r="B255" s="76"/>
-      <c r="C255" s="18"/>
-      <c r="D255" s="13"/>
-      <c r="E255" s="18"/>
-      <c r="F255" s="13"/>
-      <c r="G255" s="13"/>
-      <c r="H255" s="25"/>
-      <c r="I255" s="53"/>
-      <c r="J255" s="77"/>
-    </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A256" s="8"/>
-      <c r="B256" s="51"/>
-      <c r="C256" s="13"/>
-      <c r="D256" s="13"/>
-      <c r="E256" s="13"/>
-      <c r="F256" s="13"/>
-      <c r="G256" s="13"/>
-      <c r="H256" s="25"/>
-      <c r="I256" s="40"/>
-      <c r="J256" s="77"/>
-    </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A257" s="8"/>
-      <c r="B257" s="8"/>
-      <c r="C257" s="13"/>
-      <c r="D257" s="13"/>
-      <c r="E257" s="13"/>
-      <c r="F257" s="13"/>
-      <c r="G257" s="13"/>
-      <c r="H257" s="25"/>
-      <c r="I257" s="40"/>
-      <c r="J257" s="77"/>
-    </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A258" s="8"/>
-      <c r="B258" s="51"/>
-      <c r="C258" s="13"/>
-      <c r="D258" s="13"/>
-      <c r="E258" s="13"/>
-      <c r="F258" s="13"/>
-      <c r="G258" s="13"/>
-      <c r="H258" s="25"/>
-      <c r="I258" s="40"/>
-      <c r="J258" s="77"/>
-    </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A259" s="8"/>
-      <c r="B259" s="8"/>
-      <c r="C259" s="13"/>
-      <c r="D259" s="13"/>
-      <c r="E259" s="13"/>
-      <c r="F259" s="13"/>
-      <c r="G259" s="13"/>
-      <c r="H259" s="25"/>
-      <c r="I259" s="40"/>
-      <c r="J259" s="77"/>
-    </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A260" s="8"/>
-      <c r="B260" s="51"/>
-      <c r="C260" s="13"/>
-      <c r="D260" s="13"/>
-      <c r="E260" s="13"/>
-      <c r="F260" s="13"/>
-      <c r="G260" s="13"/>
-      <c r="H260" s="25"/>
-      <c r="I260" s="40"/>
-      <c r="J260" s="77"/>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A261" s="8"/>
-      <c r="B261" s="8"/>
-      <c r="C261" s="13"/>
-      <c r="D261" s="13"/>
-      <c r="E261" s="13"/>
-      <c r="F261" s="13"/>
-      <c r="G261" s="13"/>
-      <c r="H261" s="25"/>
-      <c r="I261" s="40"/>
-      <c r="J261" s="77"/>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A262" s="8"/>
-      <c r="B262" s="51"/>
-      <c r="C262" s="13"/>
-      <c r="D262" s="13"/>
-      <c r="E262" s="13"/>
-      <c r="F262" s="13"/>
-      <c r="G262" s="13"/>
-      <c r="H262" s="25"/>
-      <c r="I262" s="40"/>
-      <c r="J262" s="77"/>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A263" s="8"/>
-      <c r="B263" s="8"/>
-      <c r="C263" s="13"/>
-      <c r="D263" s="13"/>
-      <c r="E263" s="13"/>
-      <c r="F263" s="13"/>
-      <c r="G263" s="13"/>
-      <c r="H263" s="25"/>
-      <c r="I263" s="40"/>
-      <c r="J263" s="77"/>
-    </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A264" s="8"/>
-      <c r="B264" s="51"/>
-      <c r="C264" s="13"/>
-      <c r="D264" s="13"/>
-      <c r="E264" s="13"/>
-      <c r="F264" s="13"/>
-      <c r="G264" s="13"/>
-      <c r="H264" s="25"/>
-      <c r="I264" s="40"/>
-      <c r="J264" s="77"/>
-    </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A265" s="8"/>
-      <c r="B265" s="8"/>
-      <c r="C265" s="13"/>
-      <c r="D265" s="13"/>
-      <c r="E265" s="13"/>
-      <c r="F265" s="13"/>
-      <c r="G265" s="13"/>
-      <c r="H265" s="25"/>
-      <c r="I265" s="40"/>
-      <c r="J265" s="77"/>
-    </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A266" s="8"/>
-      <c r="B266" s="51"/>
-      <c r="C266" s="13"/>
-      <c r="D266" s="13"/>
-      <c r="E266" s="13"/>
-      <c r="F266" s="13"/>
-      <c r="G266" s="13"/>
-      <c r="H266" s="25"/>
-      <c r="I266" s="40"/>
-      <c r="J266" s="77"/>
-    </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A267" s="8"/>
-      <c r="B267" s="57"/>
-      <c r="C267" s="56"/>
-      <c r="D267" s="56"/>
-      <c r="E267" s="56"/>
-      <c r="F267" s="56"/>
-      <c r="G267" s="56"/>
-      <c r="H267" s="56"/>
-      <c r="I267" s="55"/>
-      <c r="J267" s="78"/>
-    </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A268" s="8"/>
-      <c r="B268" s="8"/>
-      <c r="C268" s="8"/>
-      <c r="D268" s="8"/>
-      <c r="E268" s="8"/>
-      <c r="F268" s="8"/>
-      <c r="G268" s="8"/>
-      <c r="H268" s="8"/>
-      <c r="I268" s="40"/>
-      <c r="J268" s="77"/>
-    </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A269" s="8"/>
-      <c r="B269" s="51"/>
-      <c r="C269" s="13"/>
-      <c r="D269" s="13"/>
-      <c r="E269" s="13"/>
-      <c r="F269" s="13"/>
-      <c r="G269" s="13"/>
-      <c r="H269" s="25"/>
-      <c r="I269" s="40"/>
-      <c r="J269" s="77"/>
-    </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A270" s="58"/>
-      <c r="B270" s="50"/>
-      <c r="C270" s="13"/>
-      <c r="D270" s="13"/>
-      <c r="E270" s="13"/>
-      <c r="F270" s="13"/>
-      <c r="G270" s="13"/>
-      <c r="H270" s="25"/>
-      <c r="I270" s="40"/>
-      <c r="J270" s="77"/>
-    </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A271" s="8"/>
-      <c r="B271" s="51"/>
-      <c r="C271" s="13"/>
-      <c r="D271" s="13"/>
-      <c r="E271" s="13"/>
-      <c r="F271" s="13"/>
-      <c r="G271" s="13"/>
-      <c r="H271" s="25"/>
-      <c r="I271" s="40"/>
-      <c r="J271" s="77"/>
-    </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A272" s="8"/>
-      <c r="B272" s="50"/>
-      <c r="C272" s="13"/>
-      <c r="D272" s="13"/>
-      <c r="E272" s="13"/>
-      <c r="F272" s="13"/>
-      <c r="G272" s="13"/>
-      <c r="H272" s="25"/>
-      <c r="I272" s="40"/>
-      <c r="J272" s="77"/>
-    </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A273" s="8"/>
-      <c r="B273" s="51"/>
-      <c r="C273" s="13"/>
-      <c r="D273" s="13"/>
-      <c r="E273" s="13"/>
-      <c r="F273" s="13"/>
-      <c r="G273" s="13"/>
-      <c r="H273" s="25"/>
-      <c r="I273" s="40"/>
-      <c r="J273" s="77"/>
-    </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A274" s="8"/>
-      <c r="B274" s="50"/>
-      <c r="C274" s="13"/>
-      <c r="D274" s="13"/>
-      <c r="E274" s="13"/>
-      <c r="F274" s="13"/>
-      <c r="G274" s="13"/>
-      <c r="H274" s="25"/>
-      <c r="I274" s="40"/>
-      <c r="J274" s="77"/>
-    </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A275" s="8"/>
-      <c r="B275" s="51"/>
-      <c r="C275" s="13"/>
-      <c r="D275" s="13"/>
-      <c r="E275" s="13"/>
-      <c r="F275" s="13"/>
-      <c r="G275" s="13"/>
-      <c r="H275" s="25"/>
-      <c r="I275" s="40"/>
-      <c r="J275" s="77"/>
-    </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A276" s="8"/>
-      <c r="B276" s="50"/>
-      <c r="C276" s="13"/>
-      <c r="D276" s="13"/>
-      <c r="E276" s="13"/>
-      <c r="F276" s="13"/>
-      <c r="G276" s="13"/>
-      <c r="H276" s="25"/>
-      <c r="I276" s="40"/>
-      <c r="J276" s="77"/>
-    </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A277" s="8"/>
-      <c r="B277" s="51"/>
-      <c r="C277" s="13"/>
-      <c r="D277" s="13"/>
-      <c r="E277" s="13"/>
-      <c r="F277" s="13"/>
-      <c r="G277" s="13"/>
-      <c r="H277" s="25"/>
-      <c r="I277" s="40"/>
-      <c r="J277" s="77"/>
-    </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A278" s="8"/>
-      <c r="B278" s="50"/>
-      <c r="C278" s="13"/>
-      <c r="D278" s="13"/>
-      <c r="E278" s="13"/>
-      <c r="F278" s="13"/>
-      <c r="G278" s="13"/>
-      <c r="H278" s="25"/>
-      <c r="I278" s="40"/>
-      <c r="J278" s="77"/>
-    </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A279" s="8"/>
-      <c r="B279" s="51"/>
-      <c r="C279" s="13"/>
-      <c r="D279" s="13"/>
-      <c r="E279" s="13"/>
-      <c r="F279" s="13"/>
-      <c r="G279" s="13"/>
-      <c r="H279" s="25"/>
-      <c r="I279" s="40"/>
-      <c r="J279" s="77"/>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A280" s="8"/>
-      <c r="B280" s="50"/>
-      <c r="C280" s="13"/>
-      <c r="D280" s="13"/>
-      <c r="E280" s="13"/>
-      <c r="F280" s="13"/>
-      <c r="G280" s="13"/>
-      <c r="H280" s="25"/>
-      <c r="I280" s="40"/>
-      <c r="J280" s="77"/>
-    </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A281" s="8"/>
-      <c r="B281" s="51"/>
-      <c r="C281" s="13"/>
-      <c r="D281" s="13"/>
-      <c r="E281" s="13"/>
-      <c r="F281" s="13"/>
-      <c r="G281" s="13"/>
-      <c r="H281" s="25"/>
-      <c r="I281" s="40"/>
-      <c r="J281" s="77"/>
-    </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A282" s="8"/>
-      <c r="B282" s="50"/>
-      <c r="C282" s="13"/>
-      <c r="D282" s="13"/>
-      <c r="E282" s="13"/>
-      <c r="F282" s="13"/>
-      <c r="G282" s="13"/>
-      <c r="H282" s="25"/>
-      <c r="I282" s="40"/>
-      <c r="J282" s="77"/>
-    </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A283" s="8"/>
-      <c r="B283" s="51"/>
-      <c r="C283" s="13"/>
-      <c r="D283" s="13"/>
-      <c r="E283" s="13"/>
-      <c r="F283" s="13"/>
-      <c r="G283" s="13"/>
-      <c r="H283" s="25"/>
-      <c r="I283" s="40"/>
-      <c r="J283" s="77"/>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A284" s="8"/>
-      <c r="B284" s="50"/>
-      <c r="C284" s="13"/>
-      <c r="D284" s="13"/>
-      <c r="E284" s="13"/>
-      <c r="F284" s="13"/>
-      <c r="G284" s="13"/>
-      <c r="H284" s="25"/>
-      <c r="I284" s="40"/>
-      <c r="J284" s="77"/>
-    </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A285" s="8"/>
-      <c r="B285" s="51"/>
-      <c r="C285" s="13"/>
-      <c r="D285" s="13"/>
-      <c r="E285" s="13"/>
-      <c r="F285" s="13"/>
-      <c r="G285" s="13"/>
-      <c r="H285" s="25"/>
-      <c r="I285" s="40"/>
-      <c r="J285" s="77"/>
-    </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A286" s="8"/>
-      <c r="B286" s="75"/>
-      <c r="C286" s="20"/>
-      <c r="D286" s="20"/>
-      <c r="E286" s="20"/>
-      <c r="F286" s="20"/>
-      <c r="G286" s="20"/>
-      <c r="H286" s="74"/>
-      <c r="I286" s="53"/>
-      <c r="J286" s="77"/>
-    </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A287" s="8"/>
-      <c r="B287" s="51"/>
-      <c r="C287" s="13"/>
-      <c r="D287" s="13"/>
-      <c r="E287" s="13"/>
-      <c r="F287" s="13"/>
-      <c r="G287" s="13"/>
-      <c r="H287" s="25"/>
-      <c r="I287" s="40"/>
-      <c r="J287" s="77"/>
-    </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A288" s="8"/>
-      <c r="B288" s="52"/>
-      <c r="C288" s="18"/>
-      <c r="D288" s="13"/>
-      <c r="E288" s="13"/>
-      <c r="F288" s="13"/>
-      <c r="G288" s="13"/>
-      <c r="H288" s="73"/>
-      <c r="I288" s="53"/>
-      <c r="J288" s="77"/>
-    </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A289" s="8"/>
-      <c r="B289" s="57"/>
-      <c r="C289" s="56"/>
-      <c r="D289" s="56"/>
-      <c r="E289" s="56"/>
-      <c r="F289" s="56"/>
-      <c r="G289" s="56"/>
-      <c r="H289" s="56"/>
-      <c r="I289" s="55"/>
-      <c r="J289" s="78"/>
-    </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A290" s="8"/>
-      <c r="B290" s="8"/>
-      <c r="C290" s="8"/>
-      <c r="D290" s="8"/>
-      <c r="E290" s="8"/>
-      <c r="F290" s="8"/>
-      <c r="G290" s="8"/>
-      <c r="H290" s="8"/>
-      <c r="I290" s="40"/>
-      <c r="J290" s="77"/>
-    </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A291" s="8"/>
-      <c r="B291" s="72"/>
-      <c r="C291" s="13"/>
-      <c r="D291" s="13"/>
-      <c r="E291" s="13"/>
-      <c r="F291" s="13"/>
-      <c r="G291" s="13"/>
-      <c r="H291" s="25"/>
-      <c r="I291" s="40"/>
-      <c r="J291" s="77"/>
-    </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A292" s="58"/>
-      <c r="B292" s="50"/>
-      <c r="C292" s="13"/>
-      <c r="D292" s="13"/>
-      <c r="E292" s="13"/>
-      <c r="F292" s="13"/>
-      <c r="G292" s="13"/>
-      <c r="H292" s="25"/>
-      <c r="I292" s="40"/>
-      <c r="J292" s="77"/>
-    </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A293" s="8"/>
-      <c r="B293" s="72"/>
-      <c r="C293" s="13"/>
-      <c r="D293" s="13"/>
-      <c r="E293" s="13"/>
-      <c r="F293" s="13"/>
-      <c r="G293" s="13"/>
-      <c r="H293" s="25"/>
-      <c r="I293" s="40"/>
-      <c r="J293" s="77"/>
-    </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A294" s="8"/>
-      <c r="B294" s="50"/>
-      <c r="C294" s="13"/>
-      <c r="D294" s="13"/>
-      <c r="E294" s="13"/>
-      <c r="F294" s="13"/>
-      <c r="G294" s="13"/>
-      <c r="H294" s="25"/>
-      <c r="I294" s="40"/>
-      <c r="J294" s="77"/>
-    </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A295" s="8"/>
-      <c r="B295" s="72"/>
-      <c r="C295" s="13"/>
-      <c r="D295" s="13"/>
-      <c r="E295" s="13"/>
-      <c r="F295" s="13"/>
-      <c r="G295" s="13"/>
-      <c r="H295" s="25"/>
-      <c r="I295" s="40"/>
-      <c r="J295" s="77"/>
-    </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A296" s="8"/>
-      <c r="B296" s="50"/>
-      <c r="C296" s="13"/>
-      <c r="D296" s="13"/>
-      <c r="E296" s="13"/>
-      <c r="F296" s="13"/>
-      <c r="G296" s="13"/>
-      <c r="H296" s="25"/>
-      <c r="I296" s="40"/>
-      <c r="J296" s="77"/>
-    </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A297" s="8"/>
-      <c r="B297" s="72"/>
-      <c r="C297" s="13"/>
-      <c r="D297" s="13"/>
-      <c r="E297" s="13"/>
-      <c r="F297" s="13"/>
-      <c r="G297" s="13"/>
-      <c r="H297" s="25"/>
-      <c r="I297" s="40"/>
-      <c r="J297" s="77"/>
-    </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A298" s="8"/>
-      <c r="B298" s="50"/>
-      <c r="C298" s="13"/>
-      <c r="D298" s="13"/>
-      <c r="E298" s="13"/>
-      <c r="F298" s="13"/>
-      <c r="G298" s="13"/>
-      <c r="H298" s="25"/>
-      <c r="I298" s="40"/>
-      <c r="J298" s="77"/>
-    </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A299" s="8"/>
-      <c r="B299" s="72"/>
-      <c r="C299" s="13"/>
-      <c r="D299" s="13"/>
-      <c r="E299" s="13"/>
-      <c r="F299" s="13"/>
-      <c r="G299" s="13"/>
-      <c r="H299" s="25"/>
-      <c r="I299" s="40"/>
-      <c r="J299" s="77"/>
-    </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A300" s="8"/>
-      <c r="B300" s="50"/>
-      <c r="C300" s="13"/>
-      <c r="D300" s="13"/>
-      <c r="E300" s="13"/>
-      <c r="F300" s="13"/>
-      <c r="G300" s="13"/>
-      <c r="H300" s="25"/>
-      <c r="I300" s="40"/>
-      <c r="J300" s="77"/>
-    </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A301" s="8"/>
-      <c r="B301" s="72"/>
-      <c r="C301" s="13"/>
-      <c r="D301" s="13"/>
-      <c r="E301" s="13"/>
-      <c r="F301" s="13"/>
-      <c r="G301" s="13"/>
-      <c r="H301" s="25"/>
-      <c r="I301" s="40"/>
-      <c r="J301" s="77"/>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A302" s="8"/>
-      <c r="B302" s="50"/>
-      <c r="C302" s="13"/>
-      <c r="D302" s="13"/>
-      <c r="E302" s="13"/>
-      <c r="F302" s="13"/>
-      <c r="G302" s="13"/>
-      <c r="H302" s="25"/>
-      <c r="I302" s="40"/>
-      <c r="J302" s="77"/>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A303" s="8"/>
-      <c r="B303" s="72"/>
-      <c r="C303" s="13"/>
-      <c r="D303" s="13"/>
-      <c r="E303" s="13"/>
-      <c r="F303" s="13"/>
-      <c r="G303" s="13"/>
-      <c r="H303" s="25"/>
-      <c r="I303" s="40"/>
-      <c r="J303" s="77"/>
-    </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A304" s="8"/>
-      <c r="B304" s="50"/>
-      <c r="C304" s="13"/>
-      <c r="D304" s="13"/>
-      <c r="E304" s="13"/>
-      <c r="F304" s="13"/>
-      <c r="G304" s="13"/>
-      <c r="H304" s="25"/>
-      <c r="I304" s="40"/>
-      <c r="J304" s="77"/>
-    </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A305" s="8"/>
-      <c r="B305" s="72"/>
-      <c r="C305" s="13"/>
-      <c r="D305" s="13"/>
-      <c r="E305" s="13"/>
-      <c r="F305" s="13"/>
-      <c r="G305" s="13"/>
-      <c r="H305" s="25"/>
-      <c r="I305" s="40"/>
-      <c r="J305" s="77"/>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A306" s="8"/>
-      <c r="B306" s="50"/>
-      <c r="C306" s="13"/>
-      <c r="D306" s="13"/>
-      <c r="E306" s="13"/>
-      <c r="F306" s="13"/>
-      <c r="G306" s="13"/>
-      <c r="H306" s="25"/>
-      <c r="I306" s="40"/>
-      <c r="J306" s="77"/>
-    </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A307" s="8"/>
-      <c r="B307" s="57"/>
-      <c r="C307" s="56"/>
-      <c r="D307" s="56"/>
-      <c r="E307" s="56"/>
-      <c r="F307" s="56"/>
-      <c r="G307" s="56"/>
-      <c r="H307" s="56"/>
-      <c r="I307" s="55"/>
-      <c r="J307" s="78"/>
-    </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A308" s="8"/>
-      <c r="B308" s="8"/>
-      <c r="C308" s="8"/>
-      <c r="D308" s="8"/>
-      <c r="E308" s="8"/>
-      <c r="F308" s="8"/>
-      <c r="G308" s="8"/>
-      <c r="H308" s="8"/>
-      <c r="I308" s="40"/>
-      <c r="J308" s="77"/>
-    </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A309" s="8"/>
-      <c r="B309" s="72"/>
-      <c r="C309" s="13"/>
-      <c r="D309" s="13"/>
-      <c r="E309" s="13"/>
-      <c r="F309" s="13"/>
-      <c r="G309" s="13"/>
-      <c r="H309" s="25"/>
-      <c r="I309" s="40"/>
-      <c r="J309" s="77"/>
-    </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A310" s="58"/>
-      <c r="B310" s="50"/>
-      <c r="C310" s="13"/>
-      <c r="D310" s="13"/>
-      <c r="E310" s="13"/>
-      <c r="F310" s="13"/>
-      <c r="G310" s="13"/>
-      <c r="H310" s="25"/>
-      <c r="I310" s="40"/>
-      <c r="J310" s="77"/>
-    </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A311" s="8"/>
-      <c r="B311" s="72"/>
-      <c r="C311" s="13"/>
-      <c r="D311" s="13"/>
-      <c r="E311" s="13"/>
-      <c r="F311" s="13"/>
-      <c r="G311" s="13"/>
-      <c r="H311" s="25"/>
-      <c r="I311" s="40"/>
-      <c r="J311" s="77"/>
-    </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A312" s="8"/>
-      <c r="B312" s="50"/>
-      <c r="C312" s="62"/>
-      <c r="D312" s="13"/>
-      <c r="E312" s="13"/>
-      <c r="F312" s="13"/>
-      <c r="G312" s="13"/>
-      <c r="H312" s="25"/>
-      <c r="I312" s="40"/>
-      <c r="J312" s="77"/>
-    </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A313" s="8"/>
-      <c r="B313" s="72"/>
-      <c r="C313" s="13"/>
-      <c r="D313" s="13"/>
-      <c r="E313" s="13"/>
-      <c r="F313" s="13"/>
-      <c r="G313" s="13"/>
-      <c r="H313" s="25"/>
-      <c r="I313" s="40"/>
-      <c r="J313" s="77"/>
-    </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A314" s="8"/>
-      <c r="B314" s="50"/>
-      <c r="C314" s="13"/>
-      <c r="D314" s="13"/>
-      <c r="E314" s="13"/>
-      <c r="F314" s="13"/>
-      <c r="G314" s="13"/>
-      <c r="H314" s="25"/>
-      <c r="I314" s="40"/>
-      <c r="J314" s="77"/>
-    </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A315" s="8"/>
-      <c r="B315" s="72"/>
-      <c r="C315" s="13"/>
-      <c r="D315" s="13"/>
-      <c r="E315" s="13"/>
-      <c r="F315" s="13"/>
-      <c r="G315" s="13"/>
-      <c r="H315" s="25"/>
-      <c r="I315" s="40"/>
-      <c r="J315" s="77"/>
-    </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A316" s="8"/>
-      <c r="B316" s="50"/>
-      <c r="C316" s="13"/>
-      <c r="D316" s="13"/>
-      <c r="E316" s="13"/>
-      <c r="F316" s="13"/>
-      <c r="G316" s="13"/>
-      <c r="H316" s="25"/>
-      <c r="I316" s="40"/>
-      <c r="J316" s="77"/>
-    </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A317" s="8"/>
-      <c r="B317" s="72"/>
-      <c r="C317" s="13"/>
-      <c r="D317" s="13"/>
-      <c r="E317" s="13"/>
-      <c r="F317" s="13"/>
-      <c r="G317" s="13"/>
-      <c r="H317" s="25"/>
-      <c r="I317" s="40"/>
-      <c r="J317" s="77"/>
-    </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A318" s="8"/>
-      <c r="B318" s="52"/>
-      <c r="C318" s="18"/>
-      <c r="D318" s="13"/>
-      <c r="E318" s="18"/>
-      <c r="F318" s="13"/>
-      <c r="G318" s="13"/>
-      <c r="H318" s="26"/>
-      <c r="I318" s="40"/>
-      <c r="J318" s="77"/>
-    </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A319" s="8"/>
-      <c r="B319" s="72"/>
-      <c r="C319" s="13"/>
-      <c r="D319" s="13"/>
-      <c r="E319" s="13"/>
-      <c r="F319" s="13"/>
-      <c r="G319" s="13"/>
-      <c r="H319" s="25"/>
-      <c r="I319" s="40"/>
-      <c r="J319" s="77"/>
-    </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A320" s="8"/>
-      <c r="B320" s="50"/>
-      <c r="C320" s="13"/>
-      <c r="D320" s="13"/>
-      <c r="E320" s="13"/>
-      <c r="F320" s="13"/>
-      <c r="G320" s="13"/>
-      <c r="H320" s="25"/>
-      <c r="I320" s="40"/>
-      <c r="J320" s="77"/>
-    </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A321" s="8"/>
-      <c r="B321" s="72"/>
-      <c r="C321" s="13"/>
-      <c r="D321" s="13"/>
-      <c r="E321" s="13"/>
-      <c r="F321" s="13"/>
-      <c r="G321" s="13"/>
-      <c r="H321" s="25"/>
-      <c r="I321" s="40"/>
-      <c r="J321" s="77"/>
-    </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A322" s="8"/>
-      <c r="B322" s="52"/>
-      <c r="C322" s="18"/>
-      <c r="D322" s="18"/>
-      <c r="E322" s="13"/>
-      <c r="F322" s="13"/>
-      <c r="G322" s="13"/>
-      <c r="H322" s="26"/>
-      <c r="I322" s="40"/>
-      <c r="J322" s="77"/>
-    </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A323" s="8"/>
-      <c r="B323" s="72"/>
-      <c r="C323" s="13"/>
-      <c r="D323" s="13"/>
-      <c r="E323" s="13"/>
-      <c r="F323" s="13"/>
-      <c r="G323" s="13"/>
-      <c r="H323" s="25"/>
-      <c r="I323" s="40"/>
-      <c r="J323" s="77"/>
-    </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A324" s="8"/>
-      <c r="B324" s="50"/>
-      <c r="C324" s="13"/>
-      <c r="D324" s="13"/>
-      <c r="E324" s="13"/>
-      <c r="F324" s="13"/>
-      <c r="G324" s="13"/>
-      <c r="H324" s="25"/>
-      <c r="I324" s="40"/>
-      <c r="J324" s="77"/>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A325" s="8"/>
-      <c r="B325" s="72"/>
-      <c r="C325" s="13"/>
-      <c r="D325" s="13"/>
-      <c r="E325" s="13"/>
-      <c r="F325" s="13"/>
-      <c r="G325" s="13"/>
-      <c r="H325" s="25"/>
-      <c r="I325" s="40"/>
-      <c r="J325" s="77"/>
-    </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A326" s="8"/>
-      <c r="B326" s="50"/>
-      <c r="C326" s="13"/>
-      <c r="D326" s="13"/>
-      <c r="E326" s="13"/>
-      <c r="F326" s="13"/>
-      <c r="G326" s="13"/>
-      <c r="H326" s="25"/>
-      <c r="I326" s="40"/>
-      <c r="J326" s="77"/>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A327" s="8"/>
-      <c r="B327" s="72"/>
-      <c r="C327" s="13"/>
-      <c r="D327" s="13"/>
-      <c r="E327" s="13"/>
-      <c r="F327" s="13"/>
-      <c r="G327" s="13"/>
-      <c r="H327" s="25"/>
-      <c r="I327" s="40"/>
-      <c r="J327" s="77"/>
-    </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A328" s="8"/>
-      <c r="B328" s="50"/>
-      <c r="C328" s="13"/>
-      <c r="D328" s="13"/>
-      <c r="E328" s="13"/>
-      <c r="F328" s="13"/>
-      <c r="G328" s="13"/>
-      <c r="H328" s="25"/>
-      <c r="I328" s="40"/>
-      <c r="J328" s="77"/>
-    </row>
-    <row r="329" spans="1:10" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="A329" s="8"/>
-      <c r="B329" s="67"/>
-      <c r="C329" s="13"/>
-      <c r="D329" s="13"/>
-      <c r="E329" s="13"/>
-      <c r="F329" s="13"/>
-      <c r="G329" s="13"/>
-      <c r="H329" s="66"/>
-      <c r="I329" s="40"/>
-      <c r="J329" s="77"/>
-    </row>
-    <row r="330" spans="1:10" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="A330" s="8"/>
-      <c r="B330" s="67"/>
-      <c r="C330" s="13"/>
-      <c r="D330" s="70"/>
-      <c r="E330" s="70"/>
-      <c r="F330" s="70"/>
-      <c r="G330" s="70"/>
-      <c r="H330" s="71"/>
-      <c r="I330" s="40"/>
-      <c r="J330" s="77"/>
-    </row>
-    <row r="331" spans="1:10" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="A331" s="8"/>
-      <c r="B331" s="67"/>
-      <c r="C331" s="68"/>
-      <c r="D331" s="68"/>
-      <c r="E331" s="68"/>
-      <c r="F331" s="68"/>
-      <c r="G331" s="68"/>
-      <c r="H331" s="69"/>
-      <c r="I331" s="40"/>
-      <c r="J331" s="77"/>
-    </row>
-    <row r="332" spans="1:10" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="A332" s="8"/>
-      <c r="B332" s="67"/>
-      <c r="C332" s="13"/>
-      <c r="D332" s="13"/>
-      <c r="E332" s="13"/>
-      <c r="F332" s="13"/>
-      <c r="G332" s="13"/>
-      <c r="H332" s="66"/>
-      <c r="I332" s="40"/>
-      <c r="J332" s="77"/>
-    </row>
-    <row r="333" spans="1:10" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="A333" s="8"/>
-      <c r="B333" s="67"/>
-      <c r="C333" s="13"/>
-      <c r="D333" s="13"/>
-      <c r="E333" s="13"/>
-      <c r="F333" s="13"/>
-      <c r="G333" s="13"/>
-      <c r="H333" s="66"/>
-      <c r="I333" s="40"/>
-      <c r="J333" s="77"/>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A334" s="8"/>
-      <c r="B334" s="57"/>
-      <c r="C334" s="56"/>
-      <c r="D334" s="56"/>
-      <c r="E334" s="56"/>
-      <c r="F334" s="56"/>
-      <c r="G334" s="56"/>
-      <c r="H334" s="56"/>
-      <c r="I334" s="55"/>
-      <c r="J334" s="78"/>
-    </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A335" s="8"/>
-      <c r="B335" s="8"/>
-      <c r="C335" s="8"/>
-      <c r="D335" s="8"/>
-      <c r="E335" s="8"/>
-      <c r="F335" s="8"/>
-      <c r="G335" s="8"/>
-      <c r="H335" s="8"/>
-      <c r="I335" s="40"/>
-      <c r="J335" s="77"/>
-    </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A336" s="8"/>
-      <c r="B336" s="65"/>
-      <c r="C336" s="13"/>
-      <c r="D336" s="13"/>
-      <c r="E336" s="13"/>
-      <c r="F336" s="13"/>
-      <c r="G336" s="13"/>
-      <c r="H336" s="25"/>
-      <c r="I336" s="40"/>
-      <c r="J336" s="77"/>
-    </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A337" s="58"/>
-      <c r="B337" s="64"/>
-      <c r="C337" s="13"/>
-      <c r="D337" s="13"/>
-      <c r="E337" s="13"/>
-      <c r="F337" s="13"/>
-      <c r="G337" s="13"/>
-      <c r="H337" s="25"/>
-      <c r="I337" s="40"/>
-      <c r="J337" s="77"/>
-    </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A338" s="8"/>
-      <c r="B338" s="65"/>
-      <c r="C338" s="13"/>
-      <c r="D338" s="13"/>
-      <c r="E338" s="13"/>
-      <c r="F338" s="13"/>
-      <c r="G338" s="13"/>
-      <c r="H338" s="25"/>
-      <c r="I338" s="40"/>
-      <c r="J338" s="77"/>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A339" s="8"/>
-      <c r="B339" s="64"/>
-      <c r="C339" s="13"/>
-      <c r="D339" s="13"/>
-      <c r="E339" s="13"/>
-      <c r="F339" s="13"/>
-      <c r="G339" s="13"/>
-      <c r="H339" s="25"/>
-      <c r="I339" s="40"/>
-      <c r="J339" s="77"/>
-    </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A340" s="8"/>
-      <c r="B340" s="57"/>
-      <c r="C340" s="56"/>
-      <c r="D340" s="56"/>
-      <c r="E340" s="56"/>
-      <c r="F340" s="56"/>
-      <c r="G340" s="56"/>
-      <c r="H340" s="56"/>
-      <c r="I340" s="55"/>
-      <c r="J340" s="78"/>
-    </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A341" s="8"/>
-      <c r="B341" s="8"/>
-      <c r="C341" s="8"/>
-      <c r="D341" s="8"/>
-      <c r="E341" s="8"/>
-      <c r="F341" s="8"/>
-      <c r="G341" s="8"/>
-      <c r="H341" s="8"/>
-      <c r="I341" s="40"/>
-      <c r="J341" s="77"/>
-    </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A342" s="8"/>
-      <c r="B342" s="54"/>
-      <c r="C342" s="18"/>
-      <c r="D342" s="13"/>
-      <c r="E342" s="13"/>
-      <c r="F342" s="22"/>
-      <c r="G342" s="13"/>
-      <c r="H342" s="25"/>
-      <c r="I342" s="53"/>
-      <c r="J342" s="77"/>
-    </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A343" s="58"/>
-      <c r="B343" s="52"/>
-      <c r="C343" s="18"/>
-      <c r="D343" s="13"/>
-      <c r="E343" s="13"/>
-      <c r="F343" s="18"/>
-      <c r="G343" s="13"/>
-      <c r="H343" s="26"/>
-      <c r="I343" s="40"/>
-      <c r="J343" s="77"/>
-    </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A344" s="8"/>
-      <c r="B344" s="54"/>
-      <c r="C344" s="18"/>
-      <c r="D344" s="13"/>
-      <c r="E344" s="13"/>
-      <c r="F344" s="18"/>
-      <c r="G344" s="13"/>
-      <c r="H344" s="26"/>
-      <c r="I344" s="40"/>
-      <c r="J344" s="77"/>
-    </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A345" s="8"/>
-      <c r="B345" s="50"/>
-      <c r="C345" s="13"/>
-      <c r="D345" s="13"/>
-      <c r="E345" s="13"/>
-      <c r="F345" s="13"/>
-      <c r="G345" s="13"/>
-      <c r="H345" s="25"/>
-      <c r="I345" s="40"/>
-      <c r="J345" s="77"/>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A346" s="8"/>
-      <c r="B346" s="54"/>
-      <c r="C346" s="18"/>
-      <c r="D346" s="62"/>
-      <c r="E346" s="62"/>
-      <c r="F346" s="13"/>
-      <c r="G346" s="13"/>
-      <c r="H346" s="63"/>
-      <c r="I346" s="40"/>
-      <c r="J346" s="77"/>
-    </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A347" s="8"/>
-      <c r="B347" s="50"/>
-      <c r="C347" s="13"/>
-      <c r="D347" s="13"/>
-      <c r="E347" s="13"/>
-      <c r="F347" s="13"/>
-      <c r="G347" s="13"/>
-      <c r="H347" s="25"/>
-      <c r="I347" s="40"/>
-      <c r="J347" s="77"/>
-    </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A348" s="8"/>
-      <c r="B348" s="51"/>
-      <c r="C348" s="13"/>
-      <c r="D348" s="13"/>
-      <c r="E348" s="13"/>
-      <c r="F348" s="13"/>
-      <c r="G348" s="13"/>
-      <c r="H348" s="25"/>
-      <c r="I348" s="40"/>
-      <c r="J348" s="77"/>
-    </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A349" s="8"/>
-      <c r="B349" s="50"/>
-      <c r="C349" s="13"/>
-      <c r="D349" s="13"/>
-      <c r="E349" s="13"/>
-      <c r="F349" s="13"/>
-      <c r="G349" s="13"/>
-      <c r="H349" s="25"/>
-      <c r="I349" s="40"/>
-      <c r="J349" s="77"/>
-    </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A350" s="8"/>
-      <c r="B350" s="51"/>
-      <c r="C350" s="13"/>
-      <c r="D350" s="13"/>
-      <c r="E350" s="13"/>
-      <c r="F350" s="13"/>
-      <c r="G350" s="13"/>
-      <c r="H350" s="25"/>
-      <c r="I350" s="40"/>
-      <c r="J350" s="77"/>
-    </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A351" s="8"/>
-      <c r="B351" s="52"/>
-      <c r="C351" s="18"/>
-      <c r="D351" s="13"/>
-      <c r="E351" s="13"/>
-      <c r="F351" s="22"/>
-      <c r="G351" s="13"/>
-      <c r="H351" s="25"/>
-      <c r="I351" s="53"/>
-      <c r="J351" s="77"/>
-    </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A352" s="8"/>
-      <c r="B352" s="51"/>
-      <c r="C352" s="13"/>
-      <c r="D352" s="13"/>
-      <c r="E352" s="13"/>
-      <c r="F352" s="13"/>
-      <c r="G352" s="13"/>
-      <c r="H352" s="25"/>
-      <c r="I352" s="40"/>
-      <c r="J352" s="77"/>
-    </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A353" s="8"/>
-      <c r="B353" s="52"/>
-      <c r="C353" s="18"/>
-      <c r="D353" s="13"/>
-      <c r="E353" s="13"/>
-      <c r="F353" s="22"/>
-      <c r="G353" s="13"/>
-      <c r="H353" s="26"/>
-      <c r="I353" s="53"/>
-      <c r="J353" s="77"/>
-    </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A354" s="8"/>
-      <c r="B354" s="51"/>
-      <c r="C354" s="13"/>
-      <c r="D354" s="13"/>
-      <c r="E354" s="13"/>
-      <c r="F354" s="13"/>
-      <c r="G354" s="13"/>
-      <c r="H354" s="25"/>
-      <c r="I354" s="40"/>
-      <c r="J354" s="77"/>
-    </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A355" s="8"/>
-      <c r="B355" s="52"/>
-      <c r="C355" s="18"/>
-      <c r="D355" s="13"/>
-      <c r="E355" s="13"/>
-      <c r="F355" s="22"/>
-      <c r="G355" s="13"/>
-      <c r="H355" s="25"/>
-      <c r="I355" s="53"/>
-      <c r="J355" s="77"/>
-    </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A356" s="8"/>
-      <c r="B356" s="54"/>
-      <c r="C356" s="18"/>
-      <c r="D356" s="13"/>
-      <c r="E356" s="13"/>
-      <c r="F356" s="18"/>
-      <c r="G356" s="13"/>
-      <c r="H356" s="26"/>
-      <c r="I356" s="40"/>
-      <c r="J356" s="77"/>
-    </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A357" s="8"/>
-      <c r="B357" s="50"/>
-      <c r="C357" s="13"/>
-      <c r="D357" s="13"/>
-      <c r="E357" s="13"/>
-      <c r="F357" s="13"/>
-      <c r="G357" s="13"/>
-      <c r="H357" s="25"/>
-      <c r="I357" s="40"/>
-      <c r="J357" s="77"/>
-    </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A358" s="8"/>
-      <c r="B358" s="51"/>
-      <c r="C358" s="13"/>
-      <c r="D358" s="13"/>
-      <c r="E358" s="13"/>
-      <c r="F358" s="13"/>
-      <c r="G358" s="13"/>
-      <c r="H358" s="25"/>
-      <c r="I358" s="40"/>
-      <c r="J358" s="77"/>
-    </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A359" s="8"/>
-      <c r="B359" s="52"/>
-      <c r="C359" s="18"/>
-      <c r="D359" s="13"/>
-      <c r="E359" s="13"/>
-      <c r="F359" s="22"/>
-      <c r="G359" s="13"/>
-      <c r="H359" s="26"/>
-      <c r="I359" s="53"/>
-      <c r="J359" s="77"/>
-    </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A360" s="8"/>
-      <c r="B360" s="54"/>
-      <c r="C360" s="18"/>
-      <c r="D360" s="13"/>
-      <c r="E360" s="13"/>
-      <c r="F360" s="22"/>
-      <c r="G360" s="13"/>
-      <c r="H360" s="26"/>
-      <c r="I360" s="53"/>
-      <c r="J360" s="77"/>
-    </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A361" s="8"/>
-      <c r="B361" s="50"/>
-      <c r="C361" s="13"/>
-      <c r="D361" s="13"/>
-      <c r="E361" s="13"/>
-      <c r="F361" s="13"/>
-      <c r="G361" s="13"/>
-      <c r="H361" s="25"/>
-      <c r="I361" s="40"/>
-      <c r="J361" s="77"/>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A362" s="8"/>
-      <c r="B362" s="54"/>
-      <c r="C362" s="18"/>
-      <c r="D362" s="13"/>
-      <c r="E362" s="13"/>
-      <c r="F362" s="18"/>
-      <c r="G362" s="13"/>
-      <c r="H362" s="26"/>
-      <c r="I362" s="40"/>
-      <c r="J362" s="77"/>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A363" s="8"/>
-      <c r="B363" s="52"/>
-      <c r="C363" s="18"/>
-      <c r="D363" s="13"/>
-      <c r="E363" s="13"/>
-      <c r="F363" s="22"/>
-      <c r="G363" s="13"/>
-      <c r="H363" s="26"/>
-      <c r="I363" s="53"/>
-      <c r="J363" s="77"/>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A364" s="8"/>
-      <c r="B364" s="54"/>
-      <c r="C364" s="18"/>
-      <c r="D364" s="13"/>
-      <c r="E364" s="13"/>
-      <c r="F364" s="22"/>
-      <c r="G364" s="13"/>
-      <c r="H364" s="25"/>
-      <c r="I364" s="53"/>
-      <c r="J364" s="77"/>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A365" s="8"/>
-      <c r="B365" s="50"/>
-      <c r="C365" s="13"/>
-      <c r="D365" s="13"/>
-      <c r="E365" s="13"/>
-      <c r="F365" s="13"/>
-      <c r="G365" s="13"/>
-      <c r="H365" s="25"/>
-      <c r="I365" s="40"/>
-      <c r="J365" s="77"/>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A366" s="8"/>
-      <c r="B366" s="51"/>
-      <c r="C366" s="13"/>
-      <c r="D366" s="13"/>
-      <c r="E366" s="13"/>
-      <c r="F366" s="13"/>
-      <c r="G366" s="13"/>
-      <c r="H366" s="25"/>
-      <c r="I366" s="40"/>
-      <c r="J366" s="77"/>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A367" s="8"/>
-      <c r="B367" s="52"/>
-      <c r="C367" s="18"/>
-      <c r="D367" s="13"/>
-      <c r="E367" s="18"/>
-      <c r="F367" s="18"/>
-      <c r="G367" s="13"/>
-      <c r="H367" s="26"/>
-      <c r="I367" s="40"/>
-      <c r="J367" s="77"/>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A368" s="8"/>
-      <c r="B368" s="54"/>
-      <c r="C368" s="18"/>
-      <c r="D368" s="13"/>
-      <c r="E368" s="13"/>
-      <c r="F368" s="22"/>
-      <c r="G368" s="13"/>
-      <c r="H368" s="25"/>
-      <c r="I368" s="53"/>
-      <c r="J368" s="77"/>
-    </row>
-    <row r="369" spans="1:10" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="A369" s="8"/>
-      <c r="B369" s="54"/>
-      <c r="C369" s="18"/>
-      <c r="D369" s="13"/>
-      <c r="E369" s="18"/>
-      <c r="F369" s="13"/>
-      <c r="G369" s="13"/>
-      <c r="H369" s="60"/>
-      <c r="I369" s="40"/>
-      <c r="J369" s="77"/>
-    </row>
-    <row r="370" spans="1:10" ht="25.5" x14ac:dyDescent="0.5">
-      <c r="A370" s="8"/>
-      <c r="B370" s="61"/>
-      <c r="C370" s="18"/>
-      <c r="D370" s="13"/>
-      <c r="E370" s="18"/>
-      <c r="F370" s="13"/>
-      <c r="G370" s="13"/>
-      <c r="H370" s="60"/>
-      <c r="I370" s="59"/>
-      <c r="J370" s="79"/>
-    </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A371" s="8"/>
-      <c r="B371" s="57"/>
-      <c r="C371" s="56"/>
-      <c r="D371" s="56"/>
-      <c r="E371" s="56"/>
-      <c r="F371" s="56"/>
-      <c r="G371" s="56"/>
-      <c r="H371" s="56"/>
-      <c r="I371" s="55"/>
-      <c r="J371" s="78"/>
-    </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A372" s="8"/>
-      <c r="B372" s="8"/>
-      <c r="C372" s="8"/>
-      <c r="D372" s="8"/>
-      <c r="E372" s="8"/>
-      <c r="F372" s="8"/>
-      <c r="G372" s="8"/>
-      <c r="H372" s="8"/>
-      <c r="I372" s="40"/>
-      <c r="J372" s="77"/>
-    </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A373" s="8"/>
-      <c r="B373" s="51"/>
-      <c r="C373" s="13"/>
-      <c r="D373" s="13"/>
-      <c r="E373" s="13"/>
-      <c r="F373" s="13"/>
-      <c r="G373" s="13"/>
-      <c r="H373" s="25"/>
-      <c r="I373" s="40"/>
-      <c r="J373" s="77"/>
-    </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A374" s="58"/>
-      <c r="B374" s="50"/>
-      <c r="C374" s="13"/>
-      <c r="D374" s="13"/>
-      <c r="E374" s="13"/>
-      <c r="F374" s="13"/>
-      <c r="G374" s="13"/>
-      <c r="H374" s="25"/>
-      <c r="I374" s="40"/>
-      <c r="J374" s="77"/>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A375" s="8"/>
-      <c r="B375" s="51"/>
-      <c r="C375" s="13"/>
-      <c r="D375" s="13"/>
-      <c r="E375" s="13"/>
-      <c r="F375" s="13"/>
-      <c r="G375" s="13"/>
-      <c r="H375" s="25"/>
-      <c r="I375" s="40"/>
-      <c r="J375" s="77"/>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A376" s="8"/>
-      <c r="B376" s="50"/>
-      <c r="C376" s="13"/>
-      <c r="D376" s="13"/>
-      <c r="E376" s="13"/>
-      <c r="F376" s="13"/>
-      <c r="G376" s="13"/>
-      <c r="H376" s="25"/>
-      <c r="I376" s="40"/>
-      <c r="J376" s="77"/>
-    </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A377" s="8"/>
-      <c r="B377" s="51"/>
-      <c r="C377" s="13"/>
-      <c r="D377" s="13"/>
-      <c r="E377" s="13"/>
-      <c r="F377" s="13"/>
-      <c r="G377" s="13"/>
-      <c r="H377" s="25"/>
-      <c r="I377" s="40"/>
-      <c r="J377" s="77"/>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A378" s="8"/>
-      <c r="B378" s="50"/>
-      <c r="C378" s="13"/>
-      <c r="D378" s="13"/>
-      <c r="E378" s="13"/>
-      <c r="F378" s="13"/>
-      <c r="G378" s="13"/>
-      <c r="H378" s="25"/>
-      <c r="I378" s="40"/>
-      <c r="J378" s="77"/>
-    </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A379" s="8"/>
-      <c r="B379" s="51"/>
-      <c r="C379" s="13"/>
-      <c r="D379" s="13"/>
-      <c r="E379" s="13"/>
-      <c r="F379" s="13"/>
-      <c r="G379" s="13"/>
-      <c r="H379" s="25"/>
-      <c r="I379" s="40"/>
-      <c r="J379" s="77"/>
-    </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A380" s="8"/>
-      <c r="B380" s="50"/>
-      <c r="C380" s="13"/>
-      <c r="D380" s="13"/>
-      <c r="E380" s="13"/>
-      <c r="F380" s="13"/>
-      <c r="G380" s="13"/>
-      <c r="H380" s="25"/>
-      <c r="I380" s="40"/>
-      <c r="J380" s="77"/>
-    </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A381" s="8"/>
-      <c r="B381" s="51"/>
-      <c r="C381" s="13"/>
-      <c r="D381" s="13"/>
-      <c r="E381" s="13"/>
-      <c r="F381" s="13"/>
-      <c r="G381" s="13"/>
-      <c r="H381" s="25"/>
-      <c r="I381" s="40"/>
-      <c r="J381" s="77"/>
-    </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A382" s="8"/>
-      <c r="B382" s="50"/>
-      <c r="C382" s="13"/>
-      <c r="D382" s="13"/>
-      <c r="E382" s="13"/>
-      <c r="F382" s="13"/>
-      <c r="G382" s="13"/>
-      <c r="H382" s="25"/>
-      <c r="I382" s="40"/>
-      <c r="J382" s="77"/>
-    </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A383" s="8"/>
-      <c r="B383" s="51"/>
-      <c r="C383" s="13"/>
-      <c r="D383" s="13"/>
-      <c r="E383" s="13"/>
-      <c r="F383" s="13"/>
-      <c r="G383" s="13"/>
-      <c r="H383" s="25"/>
-      <c r="I383" s="40"/>
-      <c r="J383" s="77"/>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A384" s="8"/>
-      <c r="B384" s="50"/>
-      <c r="C384" s="13"/>
-      <c r="D384" s="13"/>
-      <c r="E384" s="13"/>
-      <c r="F384" s="13"/>
-      <c r="G384" s="13"/>
-      <c r="H384" s="25"/>
-      <c r="I384" s="40"/>
-      <c r="J384" s="77"/>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A385" s="8"/>
-      <c r="B385" s="51"/>
-      <c r="C385" s="13"/>
-      <c r="D385" s="13"/>
-      <c r="E385" s="13"/>
-      <c r="F385" s="13"/>
-      <c r="G385" s="13"/>
-      <c r="H385" s="25"/>
-      <c r="I385" s="40"/>
-      <c r="J385" s="77"/>
-    </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A386" s="8"/>
-      <c r="B386" s="50"/>
-      <c r="C386" s="13"/>
-      <c r="D386" s="13"/>
-      <c r="E386" s="13"/>
-      <c r="F386" s="13"/>
-      <c r="G386" s="13"/>
-      <c r="H386" s="25"/>
-      <c r="I386" s="40"/>
-      <c r="J386" s="77"/>
-    </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A387" s="8"/>
-      <c r="B387" s="51"/>
-      <c r="C387" s="13"/>
-      <c r="D387" s="13"/>
-      <c r="E387" s="13"/>
-      <c r="F387" s="13"/>
-      <c r="G387" s="13"/>
-      <c r="H387" s="25"/>
-      <c r="I387" s="40"/>
-      <c r="J387" s="77"/>
-    </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A388" s="8"/>
-      <c r="B388" s="50"/>
-      <c r="C388" s="13"/>
-      <c r="D388" s="13"/>
-      <c r="E388" s="13"/>
-      <c r="F388" s="13"/>
-      <c r="G388" s="13"/>
-      <c r="H388" s="25"/>
-      <c r="I388" s="40"/>
-      <c r="J388" s="77"/>
-    </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A389" s="8"/>
-      <c r="B389" s="51"/>
-      <c r="C389" s="13"/>
-      <c r="D389" s="13"/>
-      <c r="E389" s="13"/>
-      <c r="F389" s="13"/>
-      <c r="G389" s="13"/>
-      <c r="H389" s="25"/>
-      <c r="I389" s="40"/>
-      <c r="J389" s="77"/>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A390" s="8"/>
-      <c r="B390" s="52"/>
-      <c r="C390" s="18"/>
-      <c r="D390" s="13"/>
-      <c r="E390" s="18"/>
-      <c r="F390" s="13"/>
-      <c r="G390" s="13"/>
-      <c r="H390" s="26"/>
-      <c r="I390" s="40"/>
-      <c r="J390" s="77"/>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A391" s="8"/>
-      <c r="B391" s="51"/>
-      <c r="C391" s="13"/>
-      <c r="D391" s="13"/>
-      <c r="E391" s="13"/>
-      <c r="F391" s="13"/>
-      <c r="G391" s="13"/>
-      <c r="H391" s="25"/>
-      <c r="I391" s="40"/>
-      <c r="J391" s="77"/>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A392" s="8"/>
-      <c r="B392" s="50"/>
-      <c r="C392" s="13"/>
-      <c r="D392" s="13"/>
-      <c r="E392" s="13"/>
-      <c r="F392" s="13"/>
-      <c r="G392" s="13"/>
-      <c r="H392" s="25"/>
-      <c r="I392" s="40"/>
-      <c r="J392" s="77"/>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A393" s="8"/>
-      <c r="B393" s="51"/>
-      <c r="C393" s="13"/>
-      <c r="D393" s="13"/>
-      <c r="E393" s="13"/>
-      <c r="F393" s="13"/>
-      <c r="G393" s="13"/>
-      <c r="H393" s="25"/>
-      <c r="I393" s="40"/>
-      <c r="J393" s="77"/>
-    </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A394" s="8"/>
-      <c r="B394" s="50"/>
-      <c r="C394" s="13"/>
-      <c r="D394" s="13"/>
-      <c r="E394" s="13"/>
-      <c r="F394" s="13"/>
-      <c r="G394" s="13"/>
-      <c r="H394" s="25"/>
-      <c r="I394" s="40"/>
-      <c r="J394" s="77"/>
-    </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A395" s="8"/>
-      <c r="B395" s="51"/>
-      <c r="C395" s="13"/>
-      <c r="D395" s="13"/>
-      <c r="E395" s="13"/>
-      <c r="F395" s="13"/>
-      <c r="G395" s="13"/>
-      <c r="H395" s="25"/>
-      <c r="I395" s="40"/>
-      <c r="J395" s="77"/>
-    </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A396" s="8"/>
-      <c r="B396" s="50"/>
-      <c r="C396" s="13"/>
-      <c r="D396" s="13"/>
-      <c r="E396" s="13"/>
-      <c r="F396" s="13"/>
-      <c r="G396" s="13"/>
-      <c r="H396" s="25"/>
-      <c r="I396" s="40"/>
-      <c r="J396" s="77"/>
-    </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A397" s="8"/>
-      <c r="B397" s="51"/>
-      <c r="C397" s="13"/>
-      <c r="D397" s="13"/>
-      <c r="E397" s="13"/>
-      <c r="F397" s="13"/>
-      <c r="G397" s="13"/>
-      <c r="H397" s="25"/>
-      <c r="I397" s="40"/>
-      <c r="J397" s="77"/>
-    </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A398" s="8"/>
-      <c r="B398" s="50"/>
-      <c r="C398" s="13"/>
-      <c r="D398" s="13"/>
-      <c r="E398" s="13"/>
-      <c r="F398" s="13"/>
-      <c r="G398" s="13"/>
-      <c r="H398" s="25"/>
-      <c r="I398" s="40"/>
-      <c r="J398" s="77"/>
-    </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A399" s="8"/>
-      <c r="B399" s="51"/>
-      <c r="C399" s="13"/>
-      <c r="D399" s="13"/>
-      <c r="E399" s="13"/>
-      <c r="F399" s="13"/>
-      <c r="G399" s="13"/>
-      <c r="H399" s="25"/>
-      <c r="I399" s="40"/>
-      <c r="J399" s="77"/>
-    </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A400" s="8"/>
-      <c r="B400" s="50"/>
-      <c r="C400" s="13"/>
-      <c r="D400" s="13"/>
-      <c r="E400" s="13"/>
-      <c r="F400" s="13"/>
-      <c r="G400" s="13"/>
-      <c r="H400" s="25"/>
-      <c r="I400" s="40"/>
-      <c r="J400" s="77"/>
-    </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A401" s="8"/>
-      <c r="B401" s="51"/>
-      <c r="C401" s="13"/>
-      <c r="D401" s="13"/>
-      <c r="E401" s="13"/>
-      <c r="F401" s="13"/>
-      <c r="G401" s="13"/>
-      <c r="H401" s="25"/>
-      <c r="I401" s="40"/>
-      <c r="J401" s="77"/>
-    </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A402" s="8"/>
-      <c r="B402" s="50"/>
-      <c r="C402" s="13"/>
-      <c r="D402" s="13"/>
-      <c r="E402" s="13"/>
-      <c r="F402" s="13"/>
-      <c r="G402" s="13"/>
-      <c r="H402" s="25"/>
-      <c r="I402" s="40"/>
-      <c r="J402" s="77"/>
-    </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A403" s="8"/>
-      <c r="B403" s="51"/>
-      <c r="C403" s="13"/>
-      <c r="D403" s="13"/>
-      <c r="E403" s="13"/>
-      <c r="F403" s="13"/>
-      <c r="G403" s="13"/>
-      <c r="H403" s="25"/>
-      <c r="I403" s="40"/>
-      <c r="J403" s="77"/>
-    </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A404" s="8"/>
-      <c r="B404" s="50"/>
-      <c r="C404" s="13"/>
-      <c r="D404" s="13"/>
-      <c r="E404" s="13"/>
-      <c r="F404" s="13"/>
-      <c r="G404" s="13"/>
-      <c r="H404" s="25"/>
-      <c r="I404" s="40"/>
-      <c r="J404" s="77"/>
-    </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A405" s="8"/>
-      <c r="B405" s="51"/>
-      <c r="C405" s="13"/>
-      <c r="D405" s="13"/>
-      <c r="E405" s="13"/>
-      <c r="F405" s="13"/>
-      <c r="G405" s="13"/>
-      <c r="H405" s="25"/>
-      <c r="I405" s="40"/>
-      <c r="J405" s="77"/>
-    </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A406" s="8"/>
-      <c r="B406" s="57"/>
-      <c r="C406" s="56"/>
-      <c r="D406" s="56"/>
-      <c r="E406" s="56"/>
-      <c r="F406" s="56"/>
-      <c r="G406" s="56"/>
-      <c r="H406" s="56"/>
-      <c r="I406" s="55"/>
-      <c r="J406" s="78"/>
-    </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A407" s="8"/>
-      <c r="B407" s="8"/>
-      <c r="C407" s="8"/>
-      <c r="D407" s="8"/>
-      <c r="E407" s="8"/>
-      <c r="F407" s="8"/>
-      <c r="G407" s="8"/>
-      <c r="H407" s="8"/>
-      <c r="I407" s="40"/>
-      <c r="J407" s="77"/>
-    </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A408" s="8"/>
-      <c r="B408" s="51"/>
-      <c r="C408" s="13"/>
-      <c r="D408" s="13"/>
-      <c r="E408" s="13"/>
-      <c r="F408" s="13"/>
-      <c r="G408" s="13"/>
-      <c r="H408" s="25"/>
-      <c r="I408" s="40"/>
-      <c r="J408" s="77"/>
-    </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A409" s="58"/>
-      <c r="B409" s="50"/>
-      <c r="C409" s="13"/>
-      <c r="D409" s="13"/>
-      <c r="E409" s="13"/>
-      <c r="F409" s="13"/>
-      <c r="G409" s="13"/>
-      <c r="H409" s="25"/>
-      <c r="I409" s="40"/>
-      <c r="J409" s="77"/>
-    </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A410" s="8"/>
-      <c r="B410" s="54"/>
-      <c r="C410" s="18"/>
-      <c r="D410" s="13"/>
-      <c r="E410" s="18"/>
-      <c r="F410" s="13"/>
-      <c r="G410" s="13"/>
-      <c r="H410" s="26"/>
-      <c r="I410" s="53"/>
-      <c r="J410" s="77"/>
-    </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A411" s="8"/>
-      <c r="B411" s="50"/>
-      <c r="C411" s="13"/>
-      <c r="D411" s="13"/>
-      <c r="E411" s="13"/>
-      <c r="F411" s="13"/>
-      <c r="G411" s="13"/>
-      <c r="H411" s="25"/>
-      <c r="I411" s="40"/>
-      <c r="J411" s="77"/>
-    </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A412" s="8"/>
-      <c r="B412" s="51"/>
-      <c r="C412" s="13"/>
-      <c r="D412" s="13"/>
-      <c r="E412" s="13"/>
-      <c r="F412" s="13"/>
-      <c r="G412" s="13"/>
-      <c r="H412" s="25"/>
-      <c r="I412" s="40"/>
-      <c r="J412" s="77"/>
-    </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A413" s="8"/>
-      <c r="B413" s="50"/>
-      <c r="C413" s="13"/>
-      <c r="D413" s="13"/>
-      <c r="E413" s="13"/>
-      <c r="F413" s="13"/>
-      <c r="G413" s="13"/>
-      <c r="H413" s="25"/>
-      <c r="I413" s="40"/>
-      <c r="J413" s="77"/>
-    </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A414" s="8"/>
-      <c r="B414" s="51"/>
-      <c r="C414" s="13"/>
-      <c r="D414" s="34"/>
-      <c r="E414" s="13"/>
-      <c r="F414" s="13"/>
-      <c r="G414" s="13"/>
-      <c r="H414" s="25"/>
-      <c r="I414" s="40"/>
-      <c r="J414" s="77"/>
-    </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A415" s="8"/>
-      <c r="B415" s="50"/>
-      <c r="C415" s="13"/>
-      <c r="D415" s="13"/>
-      <c r="E415" s="13"/>
-      <c r="F415" s="13"/>
-      <c r="G415" s="13"/>
-      <c r="H415" s="25"/>
-      <c r="I415" s="40"/>
-      <c r="J415" s="77"/>
-    </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A416" s="8"/>
-      <c r="B416" s="51"/>
-      <c r="C416" s="13"/>
-      <c r="D416" s="13"/>
-      <c r="E416" s="13"/>
-      <c r="F416" s="13"/>
-      <c r="G416" s="13"/>
-      <c r="H416" s="25"/>
-      <c r="I416" s="40"/>
-      <c r="J416" s="77"/>
-    </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A417" s="8"/>
-      <c r="B417" s="50"/>
-      <c r="C417" s="13"/>
-      <c r="D417" s="13"/>
-      <c r="E417" s="13"/>
-      <c r="F417" s="13"/>
-      <c r="G417" s="13"/>
-      <c r="H417" s="25"/>
-      <c r="I417" s="40"/>
-      <c r="J417" s="77"/>
-    </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A418" s="8"/>
-      <c r="B418" s="51"/>
-      <c r="C418" s="13"/>
-      <c r="D418" s="13"/>
-      <c r="E418" s="13"/>
-      <c r="F418" s="13"/>
-      <c r="G418" s="13"/>
-      <c r="H418" s="25"/>
-      <c r="I418" s="40"/>
-      <c r="J418" s="77"/>
-    </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A419" s="8"/>
-      <c r="B419" s="52"/>
-      <c r="C419" s="18"/>
-      <c r="D419" s="13"/>
-      <c r="E419" s="13"/>
-      <c r="F419" s="13"/>
-      <c r="G419" s="13"/>
-      <c r="H419" s="25"/>
-      <c r="I419" s="40"/>
-      <c r="J419" s="77"/>
-    </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A420" s="8"/>
-      <c r="B420" s="51"/>
-      <c r="C420" s="13"/>
-      <c r="D420" s="13"/>
-      <c r="E420" s="13"/>
-      <c r="F420" s="13"/>
-      <c r="G420" s="13"/>
-      <c r="H420" s="25"/>
-      <c r="I420" s="40"/>
-      <c r="J420" s="77"/>
-    </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A421" s="8"/>
-      <c r="B421" s="52"/>
-      <c r="C421" s="18"/>
-      <c r="D421" s="13"/>
-      <c r="E421" s="18"/>
-      <c r="F421" s="13"/>
-      <c r="G421" s="13"/>
-      <c r="H421" s="26"/>
-      <c r="I421" s="40"/>
-      <c r="J421" s="77"/>
-    </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A422" s="8"/>
-      <c r="B422" s="51"/>
-      <c r="C422" s="13"/>
-      <c r="D422" s="13"/>
-      <c r="E422" s="13"/>
-      <c r="F422" s="13"/>
-      <c r="G422" s="13"/>
-      <c r="H422" s="25"/>
-      <c r="I422" s="40"/>
-      <c r="J422" s="77"/>
-    </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A423" s="8"/>
-      <c r="B423" s="50"/>
-      <c r="C423" s="13"/>
-      <c r="D423" s="13"/>
-      <c r="E423" s="13"/>
-      <c r="F423" s="13"/>
-      <c r="G423" s="13"/>
-      <c r="H423" s="25"/>
-      <c r="I423" s="40"/>
-      <c r="J423" s="77"/>
-    </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A424" s="8"/>
-      <c r="B424" s="51"/>
-      <c r="C424" s="13"/>
-      <c r="D424" s="13"/>
-      <c r="E424" s="13"/>
-      <c r="F424" s="13"/>
-      <c r="G424" s="13"/>
-      <c r="H424" s="25"/>
-      <c r="I424" s="40"/>
-      <c r="J424" s="77"/>
-    </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A425" s="8"/>
-      <c r="B425" s="52"/>
-      <c r="C425" s="18"/>
-      <c r="D425" s="13"/>
-      <c r="E425" s="18"/>
-      <c r="F425" s="13"/>
-      <c r="G425" s="13"/>
-      <c r="H425" s="26"/>
-      <c r="I425" s="40"/>
-      <c r="J425" s="77"/>
-    </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A426" s="8"/>
-      <c r="B426" s="51"/>
-      <c r="C426" s="13"/>
-      <c r="D426" s="13"/>
-      <c r="E426" s="13"/>
-      <c r="F426" s="13"/>
-      <c r="G426" s="13"/>
-      <c r="H426" s="25"/>
-      <c r="I426" s="40"/>
-      <c r="J426" s="77"/>
-    </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A427" s="8"/>
-      <c r="B427" s="50"/>
-      <c r="C427" s="13"/>
-      <c r="D427" s="13"/>
-      <c r="E427" s="13"/>
-      <c r="F427" s="13"/>
-      <c r="G427" s="13"/>
-      <c r="H427" s="25"/>
-      <c r="I427" s="40"/>
-      <c r="J427" s="77"/>
-    </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A428" s="8"/>
-      <c r="B428" s="51"/>
-      <c r="C428" s="13"/>
-      <c r="D428" s="13"/>
-      <c r="E428" s="13"/>
-      <c r="F428" s="13"/>
-      <c r="G428" s="13"/>
-      <c r="H428" s="25"/>
-      <c r="I428" s="40"/>
-      <c r="J428" s="77"/>
-    </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A429" s="8"/>
-      <c r="B429" s="50"/>
-      <c r="C429" s="13"/>
-      <c r="D429" s="13"/>
-      <c r="E429" s="13"/>
-      <c r="F429" s="13"/>
-      <c r="G429" s="13"/>
-      <c r="H429" s="25"/>
-      <c r="I429" s="40"/>
-      <c r="J429" s="77"/>
-    </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A430" s="8"/>
-      <c r="B430" s="51"/>
-      <c r="C430" s="13"/>
-      <c r="D430" s="13"/>
-      <c r="E430" s="13"/>
-      <c r="F430" s="13"/>
-      <c r="G430" s="13"/>
-      <c r="H430" s="25"/>
-      <c r="I430" s="40"/>
-      <c r="J430" s="77"/>
-    </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A431" s="8"/>
-      <c r="B431" s="50"/>
-      <c r="C431" s="13"/>
-      <c r="D431" s="13"/>
-      <c r="E431" s="13"/>
-      <c r="F431" s="13"/>
-      <c r="G431" s="13"/>
-      <c r="H431" s="25"/>
-      <c r="I431" s="40"/>
-      <c r="J431" s="77"/>
-    </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A432" s="8"/>
-      <c r="B432" s="51"/>
-      <c r="C432" s="13"/>
-      <c r="D432" s="13"/>
-      <c r="E432" s="13"/>
-      <c r="F432" s="13"/>
-      <c r="G432" s="13"/>
-      <c r="H432" s="25"/>
-      <c r="I432" s="40"/>
-      <c r="J432" s="77"/>
-    </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A433" s="8"/>
-      <c r="B433" s="50"/>
-      <c r="C433" s="13"/>
-      <c r="D433" s="13"/>
-      <c r="E433" s="13"/>
-      <c r="F433" s="13"/>
-      <c r="G433" s="13"/>
-      <c r="H433" s="25"/>
-      <c r="I433" s="40"/>
-      <c r="J433" s="77"/>
-    </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A434" s="8"/>
-      <c r="B434" s="51"/>
-      <c r="C434" s="13"/>
-      <c r="D434" s="13"/>
-      <c r="E434" s="13"/>
-      <c r="F434" s="13"/>
-      <c r="G434" s="13"/>
-      <c r="H434" s="25"/>
-      <c r="I434" s="40"/>
-      <c r="J434" s="77"/>
-    </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A435" s="8"/>
-      <c r="B435" s="50"/>
-      <c r="C435" s="13"/>
-      <c r="D435" s="13"/>
-      <c r="E435" s="13"/>
-      <c r="F435" s="13"/>
-      <c r="G435" s="13"/>
-      <c r="H435" s="25"/>
-      <c r="I435" s="40"/>
-      <c r="J435" s="77"/>
-    </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A436" s="8"/>
-      <c r="B436" s="51"/>
-      <c r="C436" s="13"/>
-      <c r="D436" s="13"/>
-      <c r="E436" s="13"/>
-      <c r="F436" s="13"/>
-      <c r="G436" s="13"/>
-      <c r="H436" s="25"/>
-      <c r="I436" s="40"/>
-      <c r="J436" s="77"/>
-    </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A437" s="8"/>
-      <c r="B437" s="50"/>
-      <c r="C437" s="13"/>
-      <c r="D437" s="13"/>
-      <c r="E437" s="13"/>
-      <c r="F437" s="13"/>
-      <c r="G437" s="13"/>
-      <c r="H437" s="25"/>
-      <c r="I437" s="40"/>
-      <c r="J437" s="77"/>
-    </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A438" s="8"/>
-      <c r="B438" s="51"/>
-      <c r="C438" s="13"/>
-      <c r="D438" s="13"/>
-      <c r="E438" s="13"/>
-      <c r="F438" s="13"/>
-      <c r="G438" s="13"/>
-      <c r="H438" s="25"/>
-      <c r="I438" s="40"/>
-      <c r="J438" s="77"/>
-    </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A439" s="8"/>
-      <c r="B439" s="50"/>
-      <c r="C439" s="13"/>
-      <c r="D439" s="13"/>
-      <c r="E439" s="13"/>
-      <c r="F439" s="13"/>
-      <c r="G439" s="13"/>
-      <c r="H439" s="25"/>
-      <c r="I439" s="40"/>
-      <c r="J439" s="77"/>
-    </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A440" s="8"/>
-      <c r="B440" s="51"/>
-      <c r="C440" s="13"/>
-      <c r="D440" s="13"/>
-      <c r="E440" s="13"/>
-      <c r="F440" s="13"/>
-      <c r="G440" s="13"/>
-      <c r="H440" s="25"/>
-      <c r="I440" s="40"/>
-      <c r="J440" s="77"/>
-    </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A441" s="8"/>
-      <c r="B441" s="50"/>
-      <c r="C441" s="13"/>
-      <c r="D441" s="13"/>
-      <c r="E441" s="13"/>
-      <c r="F441" s="13"/>
-      <c r="G441" s="13"/>
-      <c r="H441" s="25"/>
-      <c r="I441" s="40"/>
-      <c r="J441" s="77"/>
-    </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A442" s="8"/>
-      <c r="B442" s="51"/>
-      <c r="C442" s="13"/>
-      <c r="D442" s="13"/>
-      <c r="E442" s="13"/>
-      <c r="F442" s="13"/>
-      <c r="G442" s="13"/>
-      <c r="H442" s="25"/>
-      <c r="I442" s="40"/>
-      <c r="J442" s="77"/>
-    </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A443" s="8"/>
-      <c r="B443" s="50"/>
-      <c r="C443" s="13"/>
-      <c r="D443" s="13"/>
-      <c r="E443" s="13"/>
-      <c r="F443" s="13"/>
-      <c r="G443" s="13"/>
-      <c r="H443" s="25"/>
-      <c r="I443" s="40"/>
-      <c r="J443" s="77"/>
-    </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A444" s="8"/>
-      <c r="B444" s="51"/>
-      <c r="C444" s="13"/>
-      <c r="D444" s="13"/>
-      <c r="E444" s="13"/>
-      <c r="F444" s="13"/>
-      <c r="G444" s="13"/>
-      <c r="H444" s="25"/>
-      <c r="I444" s="40"/>
-      <c r="J444" s="77"/>
-    </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A445" s="8"/>
-      <c r="B445" s="50"/>
-      <c r="C445" s="13"/>
-      <c r="D445" s="13"/>
-      <c r="E445" s="13"/>
-      <c r="F445" s="13"/>
-      <c r="G445" s="13"/>
-      <c r="H445" s="25"/>
-      <c r="I445" s="40"/>
-      <c r="J445" s="77"/>
-    </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A446" s="8"/>
-      <c r="B446" s="51"/>
-      <c r="C446" s="13"/>
-      <c r="D446" s="13"/>
-      <c r="E446" s="13"/>
-      <c r="F446" s="13"/>
-      <c r="G446" s="13"/>
-      <c r="H446" s="25"/>
-      <c r="I446" s="40"/>
-      <c r="J446" s="77"/>
-    </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A447" s="8"/>
-      <c r="B447" s="50"/>
-      <c r="C447" s="13"/>
-      <c r="D447" s="13"/>
-      <c r="E447" s="13"/>
-      <c r="F447" s="13"/>
-      <c r="G447" s="13"/>
-      <c r="H447" s="25"/>
-      <c r="I447" s="40"/>
-      <c r="J447" s="77"/>
-    </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A448" s="8"/>
-      <c r="B448" s="51"/>
-      <c r="C448" s="13"/>
-      <c r="D448" s="13"/>
-      <c r="E448" s="13"/>
-      <c r="F448" s="13"/>
-      <c r="G448" s="13"/>
-      <c r="H448" s="25"/>
-      <c r="I448" s="40"/>
-      <c r="J448" s="77"/>
-    </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A449" s="8"/>
-      <c r="B449" s="50"/>
-      <c r="C449" s="13"/>
-      <c r="D449" s="13"/>
-      <c r="E449" s="13"/>
-      <c r="F449" s="13"/>
-      <c r="G449" s="13"/>
-      <c r="H449" s="25"/>
-      <c r="I449" s="40"/>
-      <c r="J449" s="77"/>
-    </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A450" s="8"/>
-      <c r="B450" s="51"/>
-      <c r="C450" s="13"/>
-      <c r="D450" s="13"/>
-      <c r="E450" s="13"/>
-      <c r="F450" s="13"/>
-      <c r="G450" s="13"/>
-      <c r="H450" s="25"/>
-      <c r="I450" s="40"/>
-      <c r="J450" s="77"/>
-    </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A451" s="8"/>
-      <c r="B451" s="50"/>
-      <c r="C451" s="13"/>
-      <c r="D451" s="13"/>
-      <c r="E451" s="13"/>
-      <c r="F451" s="13"/>
-      <c r="G451" s="13"/>
-      <c r="H451" s="25"/>
-      <c r="I451" s="40"/>
-      <c r="J451" s="77"/>
-    </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A452" s="8"/>
-      <c r="B452" s="51"/>
-      <c r="C452" s="13"/>
-      <c r="D452" s="13"/>
-      <c r="E452" s="13"/>
-      <c r="F452" s="13"/>
-      <c r="G452" s="13"/>
-      <c r="H452" s="25"/>
-      <c r="I452" s="40"/>
-      <c r="J452" s="77"/>
-    </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A453" s="8"/>
-      <c r="B453" s="50"/>
-      <c r="C453" s="13"/>
-      <c r="D453" s="13"/>
-      <c r="E453" s="13"/>
-      <c r="F453" s="13"/>
-      <c r="G453" s="13"/>
-      <c r="H453" s="25"/>
-      <c r="I453" s="40"/>
-      <c r="J453" s="77"/>
-    </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A454" s="8"/>
-      <c r="B454" s="51"/>
-      <c r="C454" s="13"/>
-      <c r="D454" s="13"/>
-      <c r="E454" s="13"/>
-      <c r="F454" s="13"/>
-      <c r="G454" s="13"/>
-      <c r="H454" s="25"/>
-      <c r="I454" s="40"/>
-      <c r="J454" s="77"/>
-    </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A455" s="8"/>
-      <c r="B455" s="50"/>
-      <c r="C455" s="13"/>
-      <c r="D455" s="13"/>
-      <c r="E455" s="13"/>
-      <c r="F455" s="13"/>
-      <c r="G455" s="13"/>
-      <c r="H455" s="25"/>
-      <c r="I455" s="40"/>
-      <c r="J455" s="77"/>
-    </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A456" s="8"/>
-      <c r="B456" s="51"/>
-      <c r="C456" s="13"/>
-      <c r="D456" s="13"/>
-      <c r="E456" s="13"/>
-      <c r="F456" s="13"/>
-      <c r="G456" s="13"/>
-      <c r="H456" s="25"/>
-      <c r="I456" s="40"/>
-      <c r="J456" s="77"/>
-    </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A457" s="8"/>
-      <c r="B457" s="50"/>
-      <c r="C457" s="13"/>
-      <c r="D457" s="13"/>
-      <c r="E457" s="13"/>
-      <c r="F457" s="13"/>
-      <c r="G457" s="13"/>
-      <c r="H457" s="25"/>
-      <c r="I457" s="40"/>
-      <c r="J457" s="77"/>
-    </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A458" s="8"/>
-      <c r="B458" s="51"/>
-      <c r="C458" s="13"/>
-      <c r="D458" s="13"/>
-      <c r="E458" s="13"/>
-      <c r="F458" s="13"/>
-      <c r="G458" s="13"/>
-      <c r="H458" s="25"/>
-      <c r="I458" s="40"/>
-      <c r="J458" s="77"/>
-    </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A459" s="8"/>
-      <c r="B459" s="50"/>
-      <c r="C459" s="13"/>
-      <c r="D459" s="13"/>
-      <c r="E459" s="13"/>
-      <c r="F459" s="13"/>
-      <c r="G459" s="13"/>
-      <c r="H459" s="25"/>
-      <c r="I459" s="40"/>
-      <c r="J459" s="77"/>
-    </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A460" s="8"/>
-      <c r="B460" s="49"/>
-      <c r="C460" s="46"/>
-      <c r="D460" s="46"/>
-      <c r="E460" s="46"/>
-      <c r="F460" s="46"/>
-      <c r="G460" s="46"/>
-      <c r="H460" s="47"/>
-      <c r="I460" s="40"/>
-      <c r="J460" s="77"/>
-    </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A461" s="8"/>
-      <c r="B461" s="48"/>
-      <c r="C461" s="46"/>
-      <c r="D461" s="46"/>
-      <c r="E461" s="46"/>
-      <c r="F461" s="46"/>
-      <c r="G461" s="46"/>
-      <c r="H461" s="47"/>
-      <c r="I461" s="40"/>
-      <c r="J461" s="77"/>
-    </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A462" s="8"/>
-      <c r="B462" s="49"/>
-      <c r="C462" s="46"/>
-      <c r="D462" s="46"/>
-      <c r="E462" s="46"/>
-      <c r="F462" s="46"/>
-      <c r="G462" s="46"/>
-      <c r="H462" s="47"/>
-      <c r="I462" s="40"/>
-      <c r="J462" s="77"/>
-    </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A463" s="8"/>
-      <c r="B463" s="48"/>
-      <c r="C463" s="46"/>
-      <c r="D463" s="46"/>
-      <c r="E463" s="46"/>
-      <c r="F463" s="46"/>
-      <c r="G463" s="46"/>
-      <c r="H463" s="47"/>
-      <c r="I463" s="40"/>
-      <c r="J463" s="77"/>
-    </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A464" s="8"/>
-      <c r="B464" s="49"/>
-      <c r="C464" s="46"/>
-      <c r="D464" s="46"/>
-      <c r="E464" s="46"/>
-      <c r="F464" s="46"/>
-      <c r="G464" s="46"/>
-      <c r="H464" s="47"/>
-      <c r="I464" s="40"/>
-      <c r="J464" s="77"/>
-    </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A465" s="8"/>
-      <c r="B465" s="48"/>
-      <c r="C465" s="46"/>
-      <c r="D465" s="46"/>
-      <c r="E465" s="46"/>
-      <c r="F465" s="46"/>
-      <c r="G465" s="46"/>
-      <c r="H465" s="47"/>
-      <c r="I465" s="40"/>
-      <c r="J465" s="77"/>
-    </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A466" s="8"/>
-      <c r="B466" s="44"/>
-      <c r="C466" s="43"/>
-      <c r="D466" s="41"/>
-      <c r="E466" s="41"/>
-      <c r="F466" s="41"/>
-      <c r="G466" s="41"/>
-      <c r="H466" s="42"/>
-      <c r="I466" s="40"/>
-      <c r="J466" s="77"/>
-    </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A467" s="8"/>
-    </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A468" s="8"/>
-    </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A469" s="45"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:C466">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  <conditionalFormatting sqref="C1:C221">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.4" header="0.25" footer="0.3"/>
@@ -13528,7 +10388,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
